--- a/Banco ottico.xlsx
+++ b/Banco ottico.xlsx
@@ -401,13 +401,13 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="50">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf fontId="0" fillId="3" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="1" xfId="0" applyNumberFormat="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
       <protection hidden="0" locked="1"/>
     </xf>
@@ -472,6 +472,7 @@
     <xf fontId="0" fillId="0" borderId="13" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="5" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="7" borderId="14" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1"/>
     <xf fontId="0" fillId="0" borderId="14" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="7" borderId="15" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1969,7 +1970,7 @@
       <c r="A4" s="43">
         <v>550</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4" s="44">
         <v>146</v>
       </c>
       <c r="C4">
@@ -2009,18 +2010,18 @@
         <f t="shared" si="18"/>
         <v>107.24363636363637</v>
       </c>
-      <c r="M4" s="44">
+      <c r="M4" s="45">
         <f t="shared" si="19"/>
         <v>102.87454545454545</v>
       </c>
-      <c r="N4" s="45"/>
-      <c r="O4" s="45"/>
+      <c r="N4" s="46"/>
+      <c r="O4" s="46"/>
     </row>
     <row r="5">
       <c r="A5" s="43">
         <v>500</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5" s="44">
         <v>155</v>
       </c>
       <c r="C5">
@@ -2060,18 +2061,18 @@
         <f t="shared" si="18"/>
         <v>106.95</v>
       </c>
-      <c r="M5" s="44">
+      <c r="M5" s="45">
         <f t="shared" si="19"/>
         <v>102.95</v>
       </c>
-      <c r="N5" s="45"/>
-      <c r="O5" s="45"/>
+      <c r="N5" s="46"/>
+      <c r="O5" s="46"/>
     </row>
     <row r="6" ht="14.65">
-      <c r="A6" s="46">
+      <c r="A6" s="47">
         <v>450</v>
       </c>
-      <c r="B6" s="47">
+      <c r="B6" s="48">
         <v>173</v>
       </c>
       <c r="C6" s="26">
@@ -2111,22 +2112,22 @@
         <f t="shared" si="18"/>
         <v>106.49111111111111</v>
       </c>
-      <c r="M6" s="48">
+      <c r="M6" s="49">
         <f t="shared" si="19"/>
         <v>104.5</v>
       </c>
-      <c r="N6" s="45"/>
-      <c r="O6" s="45"/>
+      <c r="N6" s="46"/>
+      <c r="O6" s="46"/>
     </row>
     <row r="7">
-      <c r="C7" s="45"/>
-      <c r="D7" s="45"/>
+      <c r="C7" s="46"/>
+      <c r="D7" s="46"/>
     </row>
     <row r="8">
       <c r="D8" s="7"/>
     </row>
     <row r="9">
-      <c r="C9" s="45"/>
+      <c r="C9" s="46"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/Banco ottico.xlsx
+++ b/Banco ottico.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
   <si>
     <t xml:space="preserve">Lato piatto</t>
   </si>
@@ -37,6 +37,9 @@
   </si>
   <si>
     <t xml:space="preserve">sinθ rif</t>
+  </si>
+  <si>
+    <t xml:space="preserve">θ critico</t>
   </si>
   <si>
     <t>Reversibilità</t>
@@ -407,6 +410,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf fontId="0" fillId="3" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
+    <xf fontId="0" fillId="3" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="1" xfId="0" applyNumberFormat="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
       <protection hidden="0" locked="1"/>
@@ -414,7 +418,6 @@
     <xf fontId="0" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="0" fillId="3" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
     <xf fontId="0" fillId="4" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
     <xf fontId="0" fillId="5" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
@@ -1003,6 +1006,7 @@
     <col bestFit="1" min="4" max="4" width="11.125"/>
     <col bestFit="1" min="5" max="5" width="4.79296875"/>
     <col bestFit="1" min="6" max="6" width="11.125"/>
+    <col bestFit="1" min="7" max="7" width="6.875"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1022,7 +1026,7 @@
       <c r="B2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>4</v>
       </c>
       <c r="D2" s="2" t="s">
@@ -1034,9 +1038,12 @@
       <c r="F2" s="2" t="s">
         <v>5</v>
       </c>
+      <c r="G2" s="3" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="3">
+      <c r="A3" s="4">
         <v>20</v>
       </c>
       <c r="B3">
@@ -1057,26 +1064,29 @@
         <f>SIN((E3*PI())/180)</f>
         <v>0.49999999999999994</v>
       </c>
+      <c r="G3">
+        <v>44</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4">
         <v>25</v>
       </c>
-      <c r="B4" s="4">
+      <c r="B4" s="5">
         <f>SIN((A4*PI())/180)</f>
         <v>0.42261826174069944</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="5">
         <v>16</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4" s="5">
         <f>SIN((C4*PI())/180)</f>
         <v>0.27563735581699916</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E4" s="5">
         <v>39</v>
       </c>
-      <c r="F4" s="4">
+      <c r="F4" s="5">
         <f>SIN((E4*PI())/180)</f>
         <v>0.62932039104983739</v>
       </c>
@@ -1174,21 +1184,21 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="s">
-        <v>6</v>
+      <c r="A10" s="6" t="s">
+        <v>7</v>
       </c>
       <c r="B10" s="1"/>
-      <c r="C10" s="6" t="s">
-        <v>7</v>
+      <c r="C10" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="D10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E10" s="2" t="s">
-        <v>7</v>
-      </c>
       <c r="F10" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I10" s="7"/>
     </row>
@@ -1196,13 +1206,13 @@
       <c r="C11">
         <v>13</v>
       </c>
-      <c r="D11" s="4">
+      <c r="D11" s="5">
         <v>19</v>
       </c>
-      <c r="E11" s="4">
+      <c r="E11" s="5">
         <v>30</v>
       </c>
-      <c r="F11" s="4">
+      <c r="F11" s="5">
         <v>20</v>
       </c>
     </row>
@@ -1210,13 +1220,13 @@
       <c r="C12">
         <v>16</v>
       </c>
-      <c r="D12" s="4">
+      <c r="D12" s="5">
         <v>24</v>
       </c>
-      <c r="E12" s="4">
+      <c r="E12" s="5">
         <v>25</v>
       </c>
-      <c r="F12" s="4">
+      <c r="F12" s="5">
         <v>25</v>
       </c>
     </row>
@@ -1224,13 +1234,13 @@
       <c r="C13">
         <v>20</v>
       </c>
-      <c r="D13" s="4">
+      <c r="D13" s="5">
         <v>30</v>
       </c>
-      <c r="E13" s="4">
+      <c r="E13" s="5">
         <v>48</v>
       </c>
-      <c r="F13" s="4">
+      <c r="F13" s="5">
         <v>30</v>
       </c>
     </row>
@@ -1238,13 +1248,13 @@
       <c r="C14">
         <v>28</v>
       </c>
-      <c r="D14" s="4">
+      <c r="D14" s="5">
         <v>44</v>
       </c>
-      <c r="E14" s="4">
+      <c r="E14" s="5">
         <v>136</v>
       </c>
-      <c r="F14" s="4">
+      <c r="F14" s="5">
         <v>45</v>
       </c>
     </row>
@@ -1252,13 +1262,13 @@
       <c r="C15">
         <v>35</v>
       </c>
-      <c r="D15" s="4">
+      <c r="D15" s="5">
         <v>57</v>
       </c>
-      <c r="E15" s="4">
+      <c r="E15" s="5">
         <v>121</v>
       </c>
-      <c r="F15" s="4">
+      <c r="F15" s="5">
         <v>58</v>
       </c>
     </row>
@@ -1266,13 +1276,13 @@
       <c r="C16">
         <v>39</v>
       </c>
-      <c r="D16" s="4">
+      <c r="D16" s="5">
         <v>68</v>
       </c>
-      <c r="E16" s="4">
+      <c r="E16" s="5">
         <v>111</v>
       </c>
-      <c r="F16" s="4">
+      <c r="F16" s="5">
         <v>69</v>
       </c>
     </row>
@@ -1301,21 +1311,21 @@
   <sheetData>
     <row r="1">
       <c r="B1" s="8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B2">
         <f>PI()/4</f>
@@ -1336,7 +1346,7 @@
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B3">
         <f>(27*PI())/180</f>
@@ -1357,27 +1367,27 @@
     </row>
     <row r="5">
       <c r="A5" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8">
@@ -1385,7 +1395,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C8">
         <f>32*D8*(1-(E8/SQRT(D3^2-D8^2)))</f>
@@ -1405,7 +1415,7 @@
         <v>20</v>
       </c>
       <c r="B9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C9">
         <f>32*D9*(1-(E9/SQRT(D3^2-D9^2)))</f>
@@ -1425,7 +1435,7 @@
         <v>30</v>
       </c>
       <c r="B10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C10">
         <f>32*D10*(1-(E10/SQRT(D3^2-D10^2)))</f>
@@ -1445,7 +1455,7 @@
         <v>40</v>
       </c>
       <c r="B11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C11">
         <f>32*D11*(1-(E11/SQRT(D3^2-D11^2)))</f>
@@ -1465,7 +1475,7 @@
         <v>50</v>
       </c>
       <c r="B12" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C12">
         <f>32*D12*(1-(E12/SQRT(D3^2-D12^2)))</f>
@@ -1504,14 +1514,14 @@
   <sheetData>
     <row r="1" ht="14.65">
       <c r="B1" s="12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C1" s="13"/>
       <c r="D1" s="13"/>
       <c r="E1" s="13"/>
       <c r="F1" s="14"/>
       <c r="G1" s="12" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H1" s="13"/>
       <c r="I1" s="13"/>
@@ -1520,49 +1530,49 @@
     </row>
     <row r="2" ht="14.65">
       <c r="A2" s="15" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C2" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="D2" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="E2" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="G2" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="H2" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="E2" s="17" t="s">
+      <c r="I2" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="F2" s="17" t="s">
+      <c r="J2" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="G2" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="H2" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="I2" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="J2" s="17" t="s">
-        <v>33</v>
-      </c>
       <c r="K2" s="17" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="L2" s="16" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M2" s="18" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="N2" s="19" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O2" s="20" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3">
@@ -1614,10 +1624,10 @@
         <v>248.72727272727272</v>
       </c>
       <c r="N3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4">
@@ -1850,14 +1860,14 @@
   <sheetData>
     <row r="1" ht="14.65">
       <c r="B1" s="12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C1" s="13"/>
       <c r="D1" s="13"/>
       <c r="E1" s="13"/>
       <c r="F1" s="14"/>
       <c r="G1" s="28" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H1" s="29"/>
       <c r="I1" s="29"/>
@@ -1866,49 +1876,49 @@
     </row>
     <row r="2" ht="16.899999999999999" customHeight="1">
       <c r="A2" s="15" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B2" s="31" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C2" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="D2" s="33" t="s">
+        <v>42</v>
+      </c>
+      <c r="E2" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="G2" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="D2" s="33" t="s">
-        <v>41</v>
-      </c>
-      <c r="E2" s="16" t="s">
-        <v>33</v>
-      </c>
-      <c r="F2" s="18" t="s">
+      <c r="H2" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="I2" s="34" t="s">
+        <v>42</v>
+      </c>
+      <c r="J2" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="G2" s="31" t="s">
-        <v>30</v>
-      </c>
-      <c r="H2" s="32" t="s">
-        <v>31</v>
-      </c>
-      <c r="I2" s="34" t="s">
-        <v>41</v>
-      </c>
-      <c r="J2" s="16" t="s">
-        <v>33</v>
-      </c>
       <c r="K2" s="18" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="L2" s="35" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M2" s="18" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="N2" s="36" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O2" s="37" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" ht="14.65">
@@ -1960,10 +1970,10 @@
         <v>103.51833333333333</v>
       </c>
       <c r="N3" s="42" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="O3" s="42" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4">

--- a/Banco ottico.xlsx
+++ b/Banco ottico.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Angoli di rifrazione" sheetId="1" state="visible" r:id="rId1"/>
@@ -78,10 +78,10 @@
     <t>ANGOLI</t>
   </si>
   <si>
-    <t xml:space="preserve">Distanza dal centro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Distanza attesa</t>
+    <t xml:space="preserve">Distanza dal centro [mm]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Distanza attesa [mm]</t>
   </si>
   <si>
     <t>Seno</t>
@@ -404,25 +404,22 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="49">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf fontId="0" fillId="3" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
-    <xf fontId="0" fillId="3" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="1" xfId="0" applyNumberFormat="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
       <protection hidden="0" locked="1"/>
-    </xf>
-    <xf fontId="0" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
     <xf fontId="0" fillId="4" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
     <xf fontId="0" fillId="5" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" quotePrefix="1"/>
     <xf fontId="0" fillId="6" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
+    <xf fontId="0" fillId="4" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
     <xf fontId="0" fillId="4" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1026,7 +1023,7 @@
       <c r="B2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="2" t="s">
         <v>4</v>
       </c>
       <c r="D2" s="2" t="s">
@@ -1038,30 +1035,30 @@
       <c r="F2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4">
+      <c r="A3" s="3">
         <v>20</v>
       </c>
       <c r="B3">
-        <f>SIN((A3*PI())/180)</f>
+        <f t="shared" ref="B3:B8" si="0">SIN((A3*PI())/180)</f>
         <v>0.34202014332566871</v>
       </c>
       <c r="C3">
         <v>13</v>
       </c>
       <c r="D3">
-        <f>SIN((C3*PI())/180)</f>
+        <f t="shared" ref="D3:D8" si="1">SIN((C3*PI())/180)</f>
         <v>0.224951054343865</v>
       </c>
       <c r="E3">
         <v>30</v>
       </c>
       <c r="F3">
-        <f>SIN((E3*PI())/180)</f>
+        <f t="shared" ref="F3:F8" si="2">SIN((E3*PI())/180)</f>
         <v>0.49999999999999994</v>
       </c>
       <c r="G3">
@@ -1072,22 +1069,22 @@
       <c r="A4">
         <v>25</v>
       </c>
-      <c r="B4" s="5">
-        <f>SIN((A4*PI())/180)</f>
+      <c r="B4" s="4">
+        <f t="shared" si="0"/>
         <v>0.42261826174069944</v>
       </c>
-      <c r="C4" s="5">
+      <c r="C4" s="4">
         <v>16</v>
       </c>
-      <c r="D4" s="5">
-        <f>SIN((C4*PI())/180)</f>
+      <c r="D4" s="4">
+        <f t="shared" si="1"/>
         <v>0.27563735581699916</v>
       </c>
-      <c r="E4" s="5">
+      <c r="E4" s="4">
         <v>39</v>
       </c>
-      <c r="F4" s="5">
-        <f>SIN((E4*PI())/180)</f>
+      <c r="F4" s="4">
+        <f t="shared" si="2"/>
         <v>0.62932039104983739</v>
       </c>
     </row>
@@ -1096,21 +1093,21 @@
         <v>30</v>
       </c>
       <c r="B5">
-        <f>SIN((A5*PI())/180)</f>
+        <f t="shared" si="0"/>
         <v>0.49999999999999994</v>
       </c>
       <c r="C5">
         <v>20</v>
       </c>
       <c r="D5">
-        <f>SIN((C5*PI())/180)</f>
+        <f t="shared" si="1"/>
         <v>0.34202014332566871</v>
       </c>
       <c r="E5">
         <v>48</v>
       </c>
       <c r="F5">
-        <f>SIN((E5*PI())/180)</f>
+        <f t="shared" si="2"/>
         <v>0.74314482547739424</v>
       </c>
     </row>
@@ -1119,21 +1116,21 @@
         <v>45</v>
       </c>
       <c r="B6">
-        <f>SIN((A6*PI())/180)</f>
+        <f t="shared" si="0"/>
         <v>0.70710678118654746</v>
       </c>
       <c r="C6">
         <v>28</v>
       </c>
       <c r="D6">
-        <f>SIN((C6*PI())/180)</f>
+        <f t="shared" si="1"/>
         <v>0.46947156278589081</v>
       </c>
       <c r="E6">
         <v>136</v>
       </c>
       <c r="F6">
-        <f>SIN((E6*PI())/180)</f>
+        <f t="shared" si="2"/>
         <v>0.69465837045899714</v>
       </c>
     </row>
@@ -1142,21 +1139,21 @@
         <v>60</v>
       </c>
       <c r="B7">
-        <f>SIN((A7*PI())/180)</f>
+        <f t="shared" si="0"/>
         <v>0.8660254037844386</v>
       </c>
       <c r="C7">
         <v>35</v>
       </c>
       <c r="D7">
-        <f>SIN((C7*PI())/180)</f>
+        <f t="shared" si="1"/>
         <v>0.57357643635104605</v>
       </c>
       <c r="E7">
         <v>120</v>
       </c>
       <c r="F7">
-        <f>SIN((E7*PI())/180)</f>
+        <f t="shared" si="2"/>
         <v>0.86602540378443871</v>
       </c>
     </row>
@@ -1165,30 +1162,30 @@
         <v>70</v>
       </c>
       <c r="B8">
-        <f>SIN((A8*PI())/180)</f>
+        <f t="shared" si="0"/>
         <v>0.93969262078590832</v>
       </c>
       <c r="C8">
         <v>39</v>
       </c>
       <c r="D8">
-        <f>SIN((C8*PI())/180)</f>
+        <f t="shared" si="1"/>
         <v>0.62932039104983739</v>
       </c>
       <c r="E8">
         <v>111</v>
       </c>
       <c r="F8">
-        <f>SIN((E8*PI())/180)</f>
+        <f t="shared" si="2"/>
         <v>0.93358042649720174</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B10" s="1"/>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D10" s="2" t="s">
@@ -1200,19 +1197,19 @@
       <c r="F10" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="I10" s="7"/>
+      <c r="I10" s="5"/>
     </row>
     <row r="11" ht="14.25">
       <c r="C11">
         <v>13</v>
       </c>
-      <c r="D11" s="5">
+      <c r="D11" s="4">
         <v>19</v>
       </c>
-      <c r="E11" s="5">
+      <c r="E11" s="4">
         <v>30</v>
       </c>
-      <c r="F11" s="5">
+      <c r="F11" s="4">
         <v>20</v>
       </c>
     </row>
@@ -1220,13 +1217,13 @@
       <c r="C12">
         <v>16</v>
       </c>
-      <c r="D12" s="5">
+      <c r="D12" s="4">
         <v>24</v>
       </c>
-      <c r="E12" s="5">
+      <c r="E12" s="4">
         <v>25</v>
       </c>
-      <c r="F12" s="5">
+      <c r="F12" s="4">
         <v>25</v>
       </c>
     </row>
@@ -1234,13 +1231,13 @@
       <c r="C13">
         <v>20</v>
       </c>
-      <c r="D13" s="5">
+      <c r="D13" s="4">
         <v>30</v>
       </c>
-      <c r="E13" s="5">
+      <c r="E13" s="4">
         <v>48</v>
       </c>
-      <c r="F13" s="5">
+      <c r="F13" s="4">
         <v>30</v>
       </c>
     </row>
@@ -1248,13 +1245,13 @@
       <c r="C14">
         <v>28</v>
       </c>
-      <c r="D14" s="5">
+      <c r="D14" s="4">
         <v>44</v>
       </c>
-      <c r="E14" s="5">
+      <c r="E14" s="4">
         <v>136</v>
       </c>
-      <c r="F14" s="5">
+      <c r="F14" s="4">
         <v>45</v>
       </c>
     </row>
@@ -1262,13 +1259,13 @@
       <c r="C15">
         <v>35</v>
       </c>
-      <c r="D15" s="5">
+      <c r="D15" s="4">
         <v>57</v>
       </c>
-      <c r="E15" s="5">
+      <c r="E15" s="4">
         <v>121</v>
       </c>
-      <c r="F15" s="5">
+      <c r="F15" s="4">
         <v>58</v>
       </c>
     </row>
@@ -1276,13 +1273,13 @@
       <c r="C16">
         <v>39</v>
       </c>
-      <c r="D16" s="5">
+      <c r="D16" s="4">
         <v>68</v>
       </c>
-      <c r="E16" s="5">
+      <c r="E16" s="4">
         <v>111</v>
       </c>
-      <c r="F16" s="5">
+      <c r="F16" s="4">
         <v>69</v>
       </c>
     </row>
@@ -1304,19 +1301,19 @@
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="23.46484375"/>
-    <col customWidth="1" min="2" max="2" width="18.265625"/>
-    <col customWidth="1" min="3" max="3" width="15.1328125"/>
+    <col bestFit="1" customWidth="1" min="2" max="2" width="20.625"/>
+    <col bestFit="1" customWidth="1" min="3" max="3" width="17.625"/>
     <col bestFit="1" customWidth="1" min="4" max="4" width="12.33203125"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="7" t="s">
         <v>12</v>
       </c>
       <c r="E1" t="s">
@@ -1324,7 +1321,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="6" t="s">
         <v>14</v>
       </c>
       <c r="B2">
@@ -1336,16 +1333,16 @@
         <v>1.0471975511965976</v>
       </c>
       <c r="D2">
-        <f t="shared" ref="D2:D3" si="0">(SIN((B2/2)+(C2/2))/(SIN(C2/2)))</f>
+        <f t="shared" ref="D2:D3" si="3">(SIN((B2/2)+(C2/2))/(SIN(C2/2)))</f>
         <v>1.5867066805824706</v>
       </c>
-      <c r="E2" s="10">
-        <f t="shared" ref="E2:E3" si="1">((1/(2*SIN(C2/2)))*COS(((PI()/180)+C2)/2))*((PI()/180))</f>
-        <v>1.5038265780899104e-002</v>
+      <c r="E2" s="8">
+        <f>((1/(2*SIN(C2/2)))*COS(((PI()/180)+C2)/2))*((PI()/180))</f>
+        <v>1.5038265780899108e-002</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="6" t="s">
         <v>15</v>
       </c>
       <c r="B3">
@@ -1357,30 +1354,30 @@
         <v>0.78539816339744828</v>
       </c>
       <c r="D3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>1.5359568838917252</v>
       </c>
-      <c r="E3" s="10">
-        <f t="shared" si="1"/>
+      <c r="E3" s="8">
+        <f>((1/(2*SIN(C3/2)))*COS(((PI()/180)+C3)/2))*((PI()/180))</f>
         <v>2.0991032162068827e-002</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="11" t="s">
+      <c r="A5" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="9" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="10" t="s">
         <v>20</v>
       </c>
       <c r="D7" t="s">
@@ -1391,7 +1388,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="8">
+      <c r="A8" s="6">
         <v>10</v>
       </c>
       <c r="B8" t="s">
@@ -1402,16 +1399,16 @@
         <v>1.9709421734493859</v>
       </c>
       <c r="D8">
-        <f t="shared" ref="D8:D12" si="2">SIN((A8*PI())/180)</f>
+        <f t="shared" ref="D8:D12" si="4">SIN((A8*PI())/180)</f>
         <v>0.17364817766693033</v>
       </c>
       <c r="E8">
-        <f t="shared" ref="E8:E12" si="3">COS((A8*PI())/180)</f>
+        <f t="shared" ref="E8:E12" si="5">COS((A8*PI())/180)</f>
         <v>0.98480775301220802</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8">
+      <c r="A9" s="6">
         <v>20</v>
       </c>
       <c r="B9" t="s">
@@ -1422,16 +1419,16 @@
         <v>4.0763062050074748</v>
       </c>
       <c r="D9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.34202014332566871</v>
       </c>
       <c r="E9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.93969262078590843</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="8">
+      <c r="A10" s="6">
         <v>30</v>
       </c>
       <c r="B10" t="s">
@@ -1442,16 +1439,16 @@
         <v>6.4589650713431856</v>
       </c>
       <c r="D10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.49999999999999994</v>
       </c>
       <c r="E10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.86602540378443871</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8">
+      <c r="A11" s="6">
         <v>40</v>
       </c>
       <c r="B11" t="s">
@@ -1462,16 +1459,16 @@
         <v>9.2738090225061391</v>
       </c>
       <c r="D11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.64278760968653925</v>
       </c>
       <c r="E11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.76604444311897801</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="8">
+      <c r="A12" s="6">
         <v>50</v>
       </c>
       <c r="B12" t="s">
@@ -1482,11 +1479,11 @@
         <v>12.677612089302682</v>
       </c>
       <c r="D12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.76604444311897801</v>
       </c>
       <c r="E12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0.64278760968653936</v>
       </c>
     </row>
@@ -1513,114 +1510,114 @@
   </cols>
   <sheetData>
     <row r="1" ht="14.65">
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="12" t="s">
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="H1" s="13"/>
-      <c r="I1" s="13"/>
-      <c r="J1" s="13"/>
-      <c r="K1" s="13"/>
+      <c r="H1" s="12"/>
+      <c r="I1" s="12"/>
+      <c r="J1" s="12"/>
+      <c r="K1" s="12"/>
     </row>
     <row r="2" ht="14.65">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="C2" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="D2" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="E2" s="17" t="s">
+      <c r="E2" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="F2" s="17" t="s">
+      <c r="F2" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="G2" s="16" t="s">
+      <c r="G2" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="H2" s="17" t="s">
+      <c r="H2" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="I2" s="18" t="s">
+      <c r="I2" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="J2" s="17" t="s">
+      <c r="J2" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="K2" s="17" t="s">
+      <c r="K2" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="L2" s="16" t="s">
+      <c r="L2" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="M2" s="18" t="s">
+      <c r="M2" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="N2" s="19" t="s">
+      <c r="N2" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="O2" s="20" t="s">
+      <c r="O2" s="19" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="15">
+      <c r="A3" s="14">
         <v>1100</v>
       </c>
-      <c r="B3" s="21">
+      <c r="B3" s="20">
         <f>39*10</f>
         <v>390</v>
       </c>
       <c r="C3">
         <v>710</v>
       </c>
-      <c r="D3" s="22">
+      <c r="D3" s="21">
         <v>77</v>
       </c>
-      <c r="E3" s="21">
-        <f t="shared" ref="E3:E7" si="4">D3/40</f>
+      <c r="E3" s="20">
+        <f t="shared" ref="E3:E7" si="6">D3/40</f>
         <v>1.925</v>
       </c>
-      <c r="F3" s="22">
-        <f t="shared" ref="F3:F7" si="5">C3/B3</f>
+      <c r="F3" s="21">
+        <f t="shared" ref="F3:F7" si="7">C3/B3</f>
         <v>1.8205128205128205</v>
       </c>
-      <c r="G3" s="21">
+      <c r="G3" s="20">
         <v>720</v>
       </c>
       <c r="H3">
-        <f t="shared" ref="H3:H7" si="6">A3-G3</f>
+        <f t="shared" ref="H3:H7" si="8">A3-G3</f>
         <v>380</v>
       </c>
-      <c r="I3" s="22">
+      <c r="I3" s="21">
         <v>22</v>
       </c>
-      <c r="J3" s="23">
-        <f t="shared" ref="J3:J7" si="7">I3/40</f>
+      <c r="J3" s="22">
+        <f t="shared" ref="J3:J7" si="9">I3/40</f>
         <v>0.55000000000000004</v>
       </c>
-      <c r="K3" s="24">
-        <f t="shared" ref="K3:K7" si="8">H3/G3</f>
+      <c r="K3" s="23">
+        <f t="shared" ref="K3:K7" si="10">H3/G3</f>
         <v>0.52777777777777779</v>
       </c>
-      <c r="L3" s="21">
-        <f t="shared" ref="L3:L7" si="9">(B3*C3)/(B3+C3)</f>
+      <c r="L3" s="20">
+        <f t="shared" ref="L3:L7" si="11">(B3*C3)/(B3+C3)</f>
         <v>251.72727272727272</v>
       </c>
-      <c r="M3" s="22">
-        <f t="shared" ref="M3:M7" si="10">(G3*H3)/(G3+H3)</f>
+      <c r="M3" s="21">
+        <f t="shared" ref="M3:M7" si="12">(G3*H3)/(G3+H3)</f>
         <v>248.72727272727272</v>
       </c>
       <c r="N3" t="s">
@@ -1631,207 +1628,207 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="15">
+      <c r="A4" s="14">
         <v>1200</v>
       </c>
-      <c r="B4" s="21">
+      <c r="B4" s="20">
         <f>35.5*10</f>
         <v>355</v>
       </c>
       <c r="C4">
-        <f t="shared" ref="C4:C7" si="11">A4-B4</f>
+        <f t="shared" ref="C4:C7" si="13">A4-B4</f>
         <v>845</v>
       </c>
-      <c r="D4" s="22">
+      <c r="D4" s="21">
         <v>100</v>
       </c>
-      <c r="E4" s="21">
-        <f t="shared" si="4"/>
+      <c r="E4" s="20">
+        <f t="shared" si="6"/>
         <v>2.5</v>
       </c>
-      <c r="F4" s="22">
-        <f t="shared" si="5"/>
+      <c r="F4" s="21">
+        <f t="shared" si="7"/>
         <v>2.380281690140845</v>
       </c>
-      <c r="G4" s="21">
+      <c r="G4" s="20">
         <v>850</v>
       </c>
       <c r="H4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>350</v>
       </c>
-      <c r="I4" s="22">
+      <c r="I4" s="21">
         <v>18</v>
       </c>
-      <c r="J4" s="21">
-        <f t="shared" si="7"/>
+      <c r="J4" s="20">
+        <f t="shared" si="9"/>
         <v>0.45000000000000001</v>
       </c>
-      <c r="K4" s="22">
-        <f t="shared" si="8"/>
+      <c r="K4" s="21">
+        <f t="shared" si="10"/>
         <v>0.41176470588235292</v>
       </c>
-      <c r="L4" s="21">
-        <f t="shared" si="9"/>
+      <c r="L4" s="20">
+        <f t="shared" si="11"/>
         <v>249.97916666666666</v>
       </c>
-      <c r="M4" s="22">
-        <f t="shared" si="10"/>
+      <c r="M4" s="21">
+        <f t="shared" si="12"/>
         <v>247.91666666666666</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="15">
+      <c r="A5" s="14">
         <v>1300</v>
       </c>
-      <c r="B5" s="21">
+      <c r="B5" s="20">
         <f>34*10</f>
         <v>340</v>
       </c>
       <c r="C5">
+        <f t="shared" si="13"/>
+        <v>960</v>
+      </c>
+      <c r="D5" s="21">
+        <v>119</v>
+      </c>
+      <c r="E5" s="20">
+        <f t="shared" si="6"/>
+        <v>2.9750000000000001</v>
+      </c>
+      <c r="F5" s="21">
+        <f t="shared" si="7"/>
+        <v>2.8235294117647061</v>
+      </c>
+      <c r="G5" s="20">
+        <v>968</v>
+      </c>
+      <c r="H5">
+        <f t="shared" si="8"/>
+        <v>332</v>
+      </c>
+      <c r="I5" s="21">
+        <v>15</v>
+      </c>
+      <c r="J5" s="20">
+        <f t="shared" si="9"/>
+        <v>0.375</v>
+      </c>
+      <c r="K5" s="21">
+        <f t="shared" si="10"/>
+        <v>0.34297520661157027</v>
+      </c>
+      <c r="L5" s="20">
         <f t="shared" si="11"/>
-        <v>960</v>
-      </c>
-      <c r="D5" s="22">
-        <v>119</v>
-      </c>
-      <c r="E5" s="21">
-        <f t="shared" si="4"/>
-        <v>2.9750000000000001</v>
-      </c>
-      <c r="F5" s="22">
-        <f t="shared" si="5"/>
-        <v>2.8235294117647061</v>
-      </c>
-      <c r="G5" s="21">
-        <v>968</v>
-      </c>
-      <c r="H5">
-        <f t="shared" si="6"/>
-        <v>332</v>
-      </c>
-      <c r="I5" s="22">
-        <v>15</v>
-      </c>
-      <c r="J5" s="21">
-        <f t="shared" si="7"/>
-        <v>0.375</v>
-      </c>
-      <c r="K5" s="22">
-        <f t="shared" si="8"/>
-        <v>0.34297520661157027</v>
-      </c>
-      <c r="L5" s="21">
-        <f t="shared" si="9"/>
         <v>251.07692307692307</v>
       </c>
-      <c r="M5" s="22">
-        <f t="shared" si="10"/>
+      <c r="M5" s="21">
+        <f t="shared" si="12"/>
         <v>247.21230769230769</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="15">
+      <c r="A6" s="14">
         <v>1400</v>
       </c>
-      <c r="B6" s="21">
+      <c r="B6" s="20">
         <f>32.9*10</f>
         <v>329</v>
       </c>
       <c r="C6">
+        <f t="shared" si="13"/>
+        <v>1071</v>
+      </c>
+      <c r="D6" s="21">
+        <v>137</v>
+      </c>
+      <c r="E6" s="20">
+        <f t="shared" si="6"/>
+        <v>3.4249999999999998</v>
+      </c>
+      <c r="F6" s="21">
+        <f t="shared" si="7"/>
+        <v>3.2553191489361701</v>
+      </c>
+      <c r="G6" s="20">
+        <v>1074</v>
+      </c>
+      <c r="H6">
+        <f t="shared" si="8"/>
+        <v>326</v>
+      </c>
+      <c r="I6" s="21">
+        <v>13</v>
+      </c>
+      <c r="J6" s="20">
+        <f t="shared" si="9"/>
+        <v>0.32500000000000001</v>
+      </c>
+      <c r="K6" s="21">
+        <f t="shared" si="10"/>
+        <v>0.30353817504655495</v>
+      </c>
+      <c r="L6" s="20">
         <f t="shared" si="11"/>
-        <v>1071</v>
-      </c>
-      <c r="D6" s="22">
-        <v>137</v>
-      </c>
-      <c r="E6" s="21">
-        <f t="shared" si="4"/>
-        <v>3.4249999999999998</v>
-      </c>
-      <c r="F6" s="22">
-        <f t="shared" si="5"/>
-        <v>3.2553191489361701</v>
-      </c>
-      <c r="G6" s="21">
-        <v>1074</v>
-      </c>
-      <c r="H6">
-        <f t="shared" si="6"/>
-        <v>326</v>
-      </c>
-      <c r="I6" s="22">
-        <v>13</v>
-      </c>
-      <c r="J6" s="21">
-        <f t="shared" si="7"/>
-        <v>0.32500000000000001</v>
-      </c>
-      <c r="K6" s="22">
-        <f t="shared" si="8"/>
-        <v>0.30353817504655495</v>
-      </c>
-      <c r="L6" s="21">
-        <f t="shared" si="9"/>
         <v>251.685</v>
       </c>
-      <c r="M6" s="22">
-        <f t="shared" si="10"/>
+      <c r="M6" s="21">
+        <f t="shared" si="12"/>
         <v>250.08857142857144</v>
       </c>
     </row>
     <row r="7" ht="14.65">
-      <c r="A7" s="15">
+      <c r="A7" s="14">
         <v>1500</v>
       </c>
-      <c r="B7" s="25">
+      <c r="B7" s="24">
         <f>31.9*10</f>
         <v>319</v>
       </c>
-      <c r="C7" s="26">
+      <c r="C7" s="25">
+        <f t="shared" si="13"/>
+        <v>1181</v>
+      </c>
+      <c r="D7" s="26">
+        <v>155</v>
+      </c>
+      <c r="E7" s="24">
+        <f t="shared" si="6"/>
+        <v>3.875</v>
+      </c>
+      <c r="F7" s="26">
+        <f t="shared" si="7"/>
+        <v>3.7021943573667713</v>
+      </c>
+      <c r="G7" s="24">
+        <v>1186</v>
+      </c>
+      <c r="H7" s="25">
+        <f t="shared" si="8"/>
+        <v>314</v>
+      </c>
+      <c r="I7" s="26">
+        <v>12</v>
+      </c>
+      <c r="J7" s="24">
+        <f t="shared" si="9"/>
+        <v>0.29999999999999999</v>
+      </c>
+      <c r="K7" s="26">
+        <f t="shared" si="10"/>
+        <v>0.26475548060708265</v>
+      </c>
+      <c r="L7" s="24">
         <f t="shared" si="11"/>
-        <v>1181</v>
-      </c>
-      <c r="D7" s="27">
-        <v>155</v>
-      </c>
-      <c r="E7" s="25">
-        <f t="shared" si="4"/>
-        <v>3.875</v>
-      </c>
-      <c r="F7" s="27">
-        <f t="shared" si="5"/>
-        <v>3.7021943573667713</v>
-      </c>
-      <c r="G7" s="25">
-        <v>1186</v>
-      </c>
-      <c r="H7" s="26">
-        <f t="shared" si="6"/>
-        <v>314</v>
-      </c>
-      <c r="I7" s="27">
-        <v>12</v>
-      </c>
-      <c r="J7" s="25">
-        <f t="shared" si="7"/>
-        <v>0.29999999999999999</v>
-      </c>
-      <c r="K7" s="27">
-        <f t="shared" si="8"/>
-        <v>0.26475548060708265</v>
-      </c>
-      <c r="L7" s="25">
-        <f t="shared" si="9"/>
         <v>251.15933333333334</v>
       </c>
-      <c r="M7" s="27">
-        <f t="shared" si="10"/>
+      <c r="M7" s="26">
+        <f t="shared" si="12"/>
         <v>248.26933333333332</v>
       </c>
     </row>
     <row r="13">
-      <c r="L13" s="7"/>
+      <c r="L13" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1859,285 +1856,285 @@
   </cols>
   <sheetData>
     <row r="1" ht="14.65">
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="28" t="s">
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="H1" s="29"/>
-      <c r="I1" s="29"/>
-      <c r="J1" s="29"/>
-      <c r="K1" s="30"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="28"/>
+      <c r="K1" s="29"/>
     </row>
     <row r="2" ht="16.899999999999999" customHeight="1">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="31" t="s">
+      <c r="B2" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="32" t="s">
+      <c r="C2" s="31" t="s">
         <v>32</v>
       </c>
-      <c r="D2" s="33" t="s">
+      <c r="D2" s="32" t="s">
         <v>42</v>
       </c>
-      <c r="E2" s="16" t="s">
+      <c r="E2" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="F2" s="18" t="s">
+      <c r="F2" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="G2" s="31" t="s">
+      <c r="G2" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="H2" s="32" t="s">
+      <c r="H2" s="31" t="s">
         <v>32</v>
       </c>
-      <c r="I2" s="34" t="s">
+      <c r="I2" s="33" t="s">
         <v>42</v>
       </c>
-      <c r="J2" s="16" t="s">
+      <c r="J2" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="K2" s="18" t="s">
+      <c r="K2" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="L2" s="35" t="s">
+      <c r="L2" s="34" t="s">
         <v>36</v>
       </c>
-      <c r="M2" s="18" t="s">
+      <c r="M2" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="N2" s="36" t="s">
+      <c r="N2" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="O2" s="37" t="s">
+      <c r="O2" s="36" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="3" ht="14.65">
-      <c r="A3" s="38">
+      <c r="A3" s="37">
         <v>600</v>
       </c>
-      <c r="B3" s="39">
+      <c r="B3" s="38">
         <v>139</v>
       </c>
-      <c r="C3" s="40">
-        <f t="shared" ref="C3:C6" si="12">A3-B3</f>
+      <c r="C3" s="39">
+        <f t="shared" ref="C3:C6" si="14">A3-B3</f>
         <v>461</v>
       </c>
-      <c r="D3" s="24">
+      <c r="D3" s="23">
         <v>146</v>
       </c>
-      <c r="E3" s="23">
-        <f t="shared" ref="E3:E6" si="13">D3/40</f>
+      <c r="E3" s="22">
+        <f t="shared" ref="E3:E6" si="15">D3/40</f>
         <v>3.6499999999999999</v>
       </c>
-      <c r="F3" s="24">
-        <f t="shared" ref="F3:F6" si="14">C3/B3</f>
+      <c r="F3" s="23">
+        <f t="shared" ref="F3:F6" si="16">C3/B3</f>
         <v>3.3165467625899279</v>
       </c>
-      <c r="G3" s="23">
+      <c r="G3" s="22">
         <v>467</v>
       </c>
-      <c r="H3" s="40">
-        <f t="shared" ref="H3:H6" si="15">A3-G3</f>
+      <c r="H3" s="39">
+        <f t="shared" ref="H3:H6" si="17">A3-G3</f>
         <v>133</v>
       </c>
-      <c r="I3" s="24">
+      <c r="I3" s="23">
         <v>13</v>
       </c>
-      <c r="J3" s="23">
-        <f t="shared" ref="J3:J6" si="16">I3/40</f>
+      <c r="J3" s="22">
+        <f t="shared" ref="J3:J6" si="18">I3/40</f>
         <v>0.32500000000000001</v>
       </c>
-      <c r="K3" s="24">
-        <f t="shared" ref="K3:K6" si="17">H3/G3</f>
+      <c r="K3" s="23">
+        <f t="shared" ref="K3:K6" si="19">H3/G3</f>
         <v>0.28479657387580298</v>
       </c>
-      <c r="L3" s="24">
-        <f t="shared" ref="L3:L6" si="18">(B3*C3)/(B3+C3)</f>
+      <c r="L3" s="23">
+        <f t="shared" ref="L3:L6" si="20">(B3*C3)/(B3+C3)</f>
         <v>106.79833333333333</v>
       </c>
-      <c r="M3" s="41">
-        <f t="shared" ref="M3:M6" si="19">(G3*H3)/(G3+H3)</f>
+      <c r="M3" s="40">
+        <f t="shared" ref="M3:M6" si="21">(G3*H3)/(G3+H3)</f>
         <v>103.51833333333333</v>
       </c>
-      <c r="N3" s="42" t="s">
+      <c r="N3" s="41" t="s">
         <v>43</v>
       </c>
-      <c r="O3" s="42" t="s">
+      <c r="O3" s="41" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="43">
+      <c r="A4" s="42">
         <v>550</v>
       </c>
-      <c r="B4" s="44">
+      <c r="B4" s="43">
         <v>146</v>
       </c>
       <c r="C4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>404</v>
       </c>
-      <c r="D4" s="22">
+      <c r="D4" s="21">
         <v>120</v>
       </c>
-      <c r="E4" s="21">
-        <f t="shared" si="13"/>
+      <c r="E4" s="20">
+        <f t="shared" si="15"/>
         <v>3</v>
       </c>
-      <c r="F4" s="22">
+      <c r="F4" s="21">
+        <f t="shared" si="16"/>
+        <v>2.7671232876712328</v>
+      </c>
+      <c r="G4" s="20">
+        <v>413</v>
+      </c>
+      <c r="H4">
+        <f t="shared" si="17"/>
+        <v>137</v>
+      </c>
+      <c r="I4" s="21">
+        <v>15</v>
+      </c>
+      <c r="J4" s="20">
+        <f t="shared" si="18"/>
+        <v>0.375</v>
+      </c>
+      <c r="K4" s="21">
+        <f t="shared" si="19"/>
+        <v>0.33171912832929784</v>
+      </c>
+      <c r="L4" s="21">
+        <f t="shared" si="20"/>
+        <v>107.24363636363637</v>
+      </c>
+      <c r="M4" s="44">
+        <f t="shared" si="21"/>
+        <v>102.87454545454545</v>
+      </c>
+      <c r="N4" s="45"/>
+      <c r="O4" s="45"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="42">
+        <v>500</v>
+      </c>
+      <c r="B5" s="43">
+        <v>155</v>
+      </c>
+      <c r="C5">
         <f t="shared" si="14"/>
-        <v>2.7671232876712328</v>
-      </c>
-      <c r="G4" s="21">
-        <v>413</v>
-      </c>
-      <c r="H4">
+        <v>345</v>
+      </c>
+      <c r="D5" s="21">
+        <v>98</v>
+      </c>
+      <c r="E5" s="20">
         <f t="shared" si="15"/>
-        <v>137</v>
-      </c>
-      <c r="I4" s="22">
-        <v>15</v>
-      </c>
-      <c r="J4" s="21">
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="F5" s="21">
         <f t="shared" si="16"/>
-        <v>0.375</v>
-      </c>
-      <c r="K4" s="22">
+        <v>2.225806451612903</v>
+      </c>
+      <c r="G5" s="20">
+        <v>355</v>
+      </c>
+      <c r="H5">
         <f t="shared" si="17"/>
-        <v>0.33171912832929784</v>
-      </c>
-      <c r="L4" s="22">
+        <v>145</v>
+      </c>
+      <c r="I5" s="21">
+        <v>19</v>
+      </c>
+      <c r="J5" s="20">
         <f t="shared" si="18"/>
-        <v>107.24363636363637</v>
-      </c>
-      <c r="M4" s="45">
+        <v>0.47499999999999998</v>
+      </c>
+      <c r="K5" s="21">
         <f t="shared" si="19"/>
-        <v>102.87454545454545</v>
-      </c>
-      <c r="N4" s="46"/>
-      <c r="O4" s="46"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="43">
-        <v>500</v>
-      </c>
-      <c r="B5" s="44">
-        <v>155</v>
-      </c>
-      <c r="C5">
-        <f t="shared" si="12"/>
-        <v>345</v>
-      </c>
-      <c r="D5" s="22">
-        <v>98</v>
-      </c>
-      <c r="E5" s="21">
-        <f t="shared" si="13"/>
-        <v>2.4500000000000002</v>
-      </c>
-      <c r="F5" s="22">
+        <v>0.40845070422535212</v>
+      </c>
+      <c r="L5" s="21">
+        <f t="shared" si="20"/>
+        <v>106.95</v>
+      </c>
+      <c r="M5" s="44">
+        <f t="shared" si="21"/>
+        <v>102.95</v>
+      </c>
+      <c r="N5" s="45"/>
+      <c r="O5" s="45"/>
+    </row>
+    <row r="6" ht="14.65">
+      <c r="A6" s="46">
+        <v>450</v>
+      </c>
+      <c r="B6" s="47">
+        <v>173</v>
+      </c>
+      <c r="C6" s="25">
         <f t="shared" si="14"/>
-        <v>2.225806451612903</v>
-      </c>
-      <c r="G5" s="21">
-        <v>355</v>
-      </c>
-      <c r="H5">
+        <v>277</v>
+      </c>
+      <c r="D6" s="26">
+        <v>68</v>
+      </c>
+      <c r="E6" s="24">
         <f t="shared" si="15"/>
-        <v>145</v>
-      </c>
-      <c r="I5" s="22">
-        <v>19</v>
-      </c>
-      <c r="J5" s="21">
+        <v>1.7</v>
+      </c>
+      <c r="F6" s="26">
         <f t="shared" si="16"/>
-        <v>0.47499999999999998</v>
-      </c>
-      <c r="K5" s="22">
+        <v>1.6011560693641618</v>
+      </c>
+      <c r="G6" s="24">
+        <v>285</v>
+      </c>
+      <c r="H6" s="25">
         <f t="shared" si="17"/>
-        <v>0.40845070422535212</v>
-      </c>
-      <c r="L5" s="22">
+        <v>165</v>
+      </c>
+      <c r="I6" s="26">
+        <v>26</v>
+      </c>
+      <c r="J6" s="24">
         <f t="shared" si="18"/>
-        <v>106.95</v>
-      </c>
-      <c r="M5" s="45">
+        <v>0.65000000000000002</v>
+      </c>
+      <c r="K6" s="26">
         <f t="shared" si="19"/>
-        <v>102.95</v>
-      </c>
-      <c r="N5" s="46"/>
-      <c r="O5" s="46"/>
-    </row>
-    <row r="6" ht="14.65">
-      <c r="A6" s="47">
-        <v>450</v>
-      </c>
-      <c r="B6" s="48">
-        <v>173</v>
-      </c>
-      <c r="C6" s="26">
-        <f t="shared" si="12"/>
-        <v>277</v>
-      </c>
-      <c r="D6" s="27">
-        <v>68</v>
-      </c>
-      <c r="E6" s="25">
-        <f t="shared" si="13"/>
-        <v>1.7</v>
-      </c>
-      <c r="F6" s="27">
-        <f t="shared" si="14"/>
-        <v>1.6011560693641618</v>
-      </c>
-      <c r="G6" s="25">
-        <v>285</v>
-      </c>
-      <c r="H6" s="26">
-        <f t="shared" si="15"/>
-        <v>165</v>
-      </c>
-      <c r="I6" s="27">
-        <v>26</v>
-      </c>
-      <c r="J6" s="25">
-        <f t="shared" si="16"/>
-        <v>0.65000000000000002</v>
-      </c>
-      <c r="K6" s="27">
-        <f t="shared" si="17"/>
         <v>0.57894736842105265</v>
       </c>
-      <c r="L6" s="27">
-        <f t="shared" si="18"/>
+      <c r="L6" s="26">
+        <f t="shared" si="20"/>
         <v>106.49111111111111</v>
       </c>
-      <c r="M6" s="49">
-        <f t="shared" si="19"/>
+      <c r="M6" s="48">
+        <f t="shared" si="21"/>
         <v>104.5</v>
       </c>
-      <c r="N6" s="46"/>
-      <c r="O6" s="46"/>
+      <c r="N6" s="45"/>
+      <c r="O6" s="45"/>
     </row>
     <row r="7">
-      <c r="C7" s="46"/>
-      <c r="D7" s="46"/>
+      <c r="C7" s="45"/>
+      <c r="D7" s="45"/>
     </row>
     <row r="8">
-      <c r="D8" s="7"/>
+      <c r="D8" s="5"/>
     </row>
     <row r="9">
-      <c r="C9" s="46"/>
+      <c r="C9" s="45"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/Banco ottico.xlsx
+++ b/Banco ottico.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
   <si>
     <t xml:space="preserve">Lato piatto</t>
   </si>
@@ -88,21 +88,6 @@
   </si>
   <si>
     <t>Coseno</t>
-  </si>
-  <si>
-    <t>2mm</t>
-  </si>
-  <si>
-    <t>4mm</t>
-  </si>
-  <si>
-    <t>6mm</t>
-  </si>
-  <si>
-    <t>9mm</t>
-  </si>
-  <si>
-    <t>12mm</t>
   </si>
   <si>
     <t xml:space="preserve">Fuoco 1</t>
@@ -1391,8 +1376,8 @@
       <c r="A8" s="6">
         <v>10</v>
       </c>
-      <c r="B8" t="s">
-        <v>23</v>
+      <c r="B8">
+        <v>2</v>
       </c>
       <c r="C8">
         <f>32*D8*(1-(E8/SQRT(D3^2-D8^2)))</f>
@@ -1411,8 +1396,8 @@
       <c r="A9" s="6">
         <v>20</v>
       </c>
-      <c r="B9" t="s">
-        <v>24</v>
+      <c r="B9">
+        <v>4</v>
       </c>
       <c r="C9">
         <f>32*D9*(1-(E9/SQRT(D3^2-D9^2)))</f>
@@ -1431,8 +1416,8 @@
       <c r="A10" s="6">
         <v>30</v>
       </c>
-      <c r="B10" t="s">
-        <v>25</v>
+      <c r="B10">
+        <v>6</v>
       </c>
       <c r="C10">
         <f>32*D10*(1-(E10/SQRT(D3^2-D10^2)))</f>
@@ -1451,8 +1436,8 @@
       <c r="A11" s="6">
         <v>40</v>
       </c>
-      <c r="B11" t="s">
-        <v>26</v>
+      <c r="B11">
+        <v>9</v>
       </c>
       <c r="C11">
         <f>32*D11*(1-(E11/SQRT(D3^2-D11^2)))</f>
@@ -1471,8 +1456,8 @@
       <c r="A12" s="6">
         <v>50</v>
       </c>
-      <c r="B12" t="s">
-        <v>27</v>
+      <c r="B12">
+        <v>12</v>
       </c>
       <c r="C12">
         <f>32*D12*(1-(E12/SQRT(D3^2-D12^2)))</f>
@@ -1511,14 +1496,14 @@
   <sheetData>
     <row r="1" ht="14.65">
       <c r="B1" s="11" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C1" s="12"/>
       <c r="D1" s="12"/>
       <c r="E1" s="12"/>
       <c r="F1" s="13"/>
       <c r="G1" s="11" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="H1" s="12"/>
       <c r="I1" s="12"/>
@@ -1527,49 +1512,49 @@
     </row>
     <row r="2" ht="14.65">
       <c r="A2" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="E2" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="F2" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="G2" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="H2" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I2" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="J2" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="K2" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="L2" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="16" t="s">
+      <c r="M2" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="D2" s="17" t="s">
+      <c r="N2" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="E2" s="16" t="s">
+      <c r="O2" s="19" t="s">
         <v>34</v>
-      </c>
-      <c r="F2" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="G2" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="H2" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="I2" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="J2" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="K2" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="L2" s="15" t="s">
-        <v>36</v>
-      </c>
-      <c r="M2" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="N2" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="O2" s="19" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="3">
@@ -1621,10 +1606,10 @@
         <v>248.72727272727272</v>
       </c>
       <c r="N3" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="O3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4">
@@ -1857,14 +1842,14 @@
   <sheetData>
     <row r="1" ht="14.65">
       <c r="B1" s="11" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C1" s="12"/>
       <c r="D1" s="12"/>
       <c r="E1" s="12"/>
       <c r="F1" s="13"/>
       <c r="G1" s="27" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="H1" s="28"/>
       <c r="I1" s="28"/>
@@ -1873,49 +1858,49 @@
     </row>
     <row r="2" ht="16.899999999999999" customHeight="1">
       <c r="A2" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" s="30" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2" s="32" t="s">
+        <v>37</v>
+      </c>
+      <c r="E2" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="F2" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="30" t="s">
+      <c r="G2" s="30" t="s">
+        <v>26</v>
+      </c>
+      <c r="H2" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="I2" s="33" t="s">
+        <v>37</v>
+      </c>
+      <c r="J2" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="K2" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="L2" s="34" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="31" t="s">
+      <c r="M2" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="D2" s="32" t="s">
-        <v>42</v>
-      </c>
-      <c r="E2" s="15" t="s">
+      <c r="N2" s="35" t="s">
+        <v>33</v>
+      </c>
+      <c r="O2" s="36" t="s">
         <v>34</v>
-      </c>
-      <c r="F2" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="G2" s="30" t="s">
-        <v>31</v>
-      </c>
-      <c r="H2" s="31" t="s">
-        <v>32</v>
-      </c>
-      <c r="I2" s="33" t="s">
-        <v>42</v>
-      </c>
-      <c r="J2" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="K2" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="L2" s="34" t="s">
-        <v>36</v>
-      </c>
-      <c r="M2" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="N2" s="35" t="s">
-        <v>38</v>
-      </c>
-      <c r="O2" s="36" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="3" ht="14.65">
@@ -1967,10 +1952,10 @@
         <v>103.51833333333333</v>
       </c>
       <c r="N3" s="41" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O3" s="41" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4">

--- a/Banco ottico.xlsx
+++ b/Banco ottico.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="1"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Angoli di rifrazione" sheetId="1" state="visible" r:id="rId1"/>
@@ -1510,7 +1510,7 @@
       <c r="J1" s="12"/>
       <c r="K1" s="12"/>
     </row>
-    <row r="2" ht="14.65">
+    <row r="2" ht="28.5">
       <c r="A2" s="14" t="s">
         <v>25</v>
       </c>

--- a/Banco ottico.xlsx
+++ b/Banco ottico.xlsx
@@ -389,7 +389,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="48">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -404,7 +404,6 @@
     <xf fontId="0" fillId="5" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" quotePrefix="1"/>
     <xf fontId="0" fillId="6" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
-    <xf fontId="0" fillId="4" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
     <xf fontId="0" fillId="4" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1322,7 +1321,7 @@
         <v>1.5867066805824706</v>
       </c>
       <c r="E2" s="8">
-        <f>((1/(2*SIN(C2/2)))*COS(((PI()/180)+C2)/2))*((PI()/180))</f>
+        <f t="shared" ref="E2:E3" si="4">((1/(2*SIN(C2/2)))*COS(((PI()/180)+C2)/2))*((PI()/180))</f>
         <v>1.5038265780899108e-002</v>
       </c>
     </row>
@@ -1343,7 +1342,7 @@
         <v>1.5359568838917252</v>
       </c>
       <c r="E3" s="8">
-        <f>((1/(2*SIN(C3/2)))*COS(((PI()/180)+C3)/2))*((PI()/180))</f>
+        <f t="shared" si="4"/>
         <v>2.0991032162068827e-002</v>
       </c>
     </row>
@@ -1359,10 +1358,10 @@
       <c r="A7" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="10" t="s">
+      <c r="B7" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D7" t="s">
@@ -1384,11 +1383,11 @@
         <v>1.9709421734493859</v>
       </c>
       <c r="D8">
-        <f t="shared" ref="D8:D12" si="4">SIN((A8*PI())/180)</f>
+        <f t="shared" ref="D8:D12" si="5">SIN((A8*PI())/180)</f>
         <v>0.17364817766693033</v>
       </c>
       <c r="E8">
-        <f t="shared" ref="E8:E12" si="5">COS((A8*PI())/180)</f>
+        <f t="shared" ref="E8:E12" si="6">COS((A8*PI())/180)</f>
         <v>0.98480775301220802</v>
       </c>
     </row>
@@ -1404,11 +1403,11 @@
         <v>4.0763062050074748</v>
       </c>
       <c r="D9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.34202014332566871</v>
       </c>
       <c r="E9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.93969262078590843</v>
       </c>
     </row>
@@ -1424,11 +1423,11 @@
         <v>6.4589650713431856</v>
       </c>
       <c r="D10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.49999999999999994</v>
       </c>
       <c r="E10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.86602540378443871</v>
       </c>
     </row>
@@ -1444,11 +1443,11 @@
         <v>9.2738090225061391</v>
       </c>
       <c r="D11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.64278760968653925</v>
       </c>
       <c r="E11">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.76604444311897801</v>
       </c>
     </row>
@@ -1464,11 +1463,11 @@
         <v>12.677612089302682</v>
       </c>
       <c r="D12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.76604444311897801</v>
       </c>
       <c r="E12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.64278760968653936</v>
       </c>
     </row>
@@ -1495,113 +1494,113 @@
   </cols>
   <sheetData>
     <row r="1" ht="14.65">
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="11" t="s">
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="H1" s="12"/>
-      <c r="I1" s="12"/>
-      <c r="J1" s="12"/>
-      <c r="K1" s="12"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="11"/>
+      <c r="K1" s="11"/>
     </row>
     <row r="2" ht="28.5">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="C2" s="16" t="s">
+      <c r="C2" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="D2" s="17" t="s">
+      <c r="D2" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="E2" s="16" t="s">
+      <c r="E2" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="F2" s="16" t="s">
+      <c r="F2" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="G2" s="15" t="s">
+      <c r="G2" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="H2" s="16" t="s">
+      <c r="H2" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="I2" s="17" t="s">
+      <c r="I2" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="J2" s="16" t="s">
+      <c r="J2" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="K2" s="16" t="s">
+      <c r="K2" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="L2" s="15" t="s">
+      <c r="L2" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="M2" s="17" t="s">
+      <c r="M2" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="N2" s="18" t="s">
+      <c r="N2" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="O2" s="19" t="s">
+      <c r="O2" s="18" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="14">
+      <c r="A3" s="13">
         <v>1100</v>
       </c>
-      <c r="B3" s="20">
+      <c r="B3" s="19">
         <f>39*10</f>
         <v>390</v>
       </c>
       <c r="C3">
         <v>710</v>
       </c>
-      <c r="D3" s="21">
+      <c r="D3" s="20">
         <v>77</v>
       </c>
-      <c r="E3" s="20">
-        <f t="shared" ref="E3:E7" si="6">D3/40</f>
+      <c r="E3" s="19">
+        <f>D3/40</f>
         <v>1.925</v>
       </c>
-      <c r="F3" s="21">
+      <c r="F3" s="20">
         <f t="shared" ref="F3:F7" si="7">C3/B3</f>
         <v>1.8205128205128205</v>
       </c>
-      <c r="G3" s="20">
+      <c r="G3" s="19">
         <v>720</v>
       </c>
       <c r="H3">
         <f t="shared" ref="H3:H7" si="8">A3-G3</f>
         <v>380</v>
       </c>
-      <c r="I3" s="21">
+      <c r="I3" s="20">
         <v>22</v>
       </c>
-      <c r="J3" s="22">
+      <c r="J3" s="21">
         <f t="shared" ref="J3:J7" si="9">I3/40</f>
         <v>0.55000000000000004</v>
       </c>
-      <c r="K3" s="23">
+      <c r="K3" s="22">
         <f t="shared" ref="K3:K7" si="10">H3/G3</f>
         <v>0.52777777777777779</v>
       </c>
-      <c r="L3" s="20">
+      <c r="L3" s="19">
         <f t="shared" ref="L3:L7" si="11">(B3*C3)/(B3+C3)</f>
         <v>251.72727272727272</v>
       </c>
-      <c r="M3" s="21">
+      <c r="M3" s="20">
         <f t="shared" ref="M3:M7" si="12">(G3*H3)/(G3+H3)</f>
         <v>248.72727272727272</v>
       </c>
@@ -1613,10 +1612,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="14">
+      <c r="A4" s="13">
         <v>1200</v>
       </c>
-      <c r="B4" s="20">
+      <c r="B4" s="19">
         <f>35.5*10</f>
         <v>355</v>
       </c>
@@ -1624,49 +1623,49 @@
         <f t="shared" ref="C4:C7" si="13">A4-B4</f>
         <v>845</v>
       </c>
-      <c r="D4" s="21">
+      <c r="D4" s="20">
         <v>100</v>
       </c>
-      <c r="E4" s="20">
-        <f t="shared" si="6"/>
+      <c r="E4" s="19">
+        <f t="shared" ref="E4:E7" si="14">D4/40</f>
         <v>2.5</v>
       </c>
-      <c r="F4" s="21">
+      <c r="F4" s="20">
         <f t="shared" si="7"/>
         <v>2.380281690140845</v>
       </c>
-      <c r="G4" s="20">
+      <c r="G4" s="19">
         <v>850</v>
       </c>
       <c r="H4">
         <f t="shared" si="8"/>
         <v>350</v>
       </c>
-      <c r="I4" s="21">
+      <c r="I4" s="20">
         <v>18</v>
       </c>
-      <c r="J4" s="20">
+      <c r="J4" s="19">
         <f t="shared" si="9"/>
         <v>0.45000000000000001</v>
       </c>
-      <c r="K4" s="21">
+      <c r="K4" s="20">
         <f t="shared" si="10"/>
         <v>0.41176470588235292</v>
       </c>
-      <c r="L4" s="20">
+      <c r="L4" s="19">
         <f t="shared" si="11"/>
         <v>249.97916666666666</v>
       </c>
-      <c r="M4" s="21">
+      <c r="M4" s="20">
         <f t="shared" si="12"/>
         <v>247.91666666666666</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="14">
+      <c r="A5" s="13">
         <v>1300</v>
       </c>
-      <c r="B5" s="20">
+      <c r="B5" s="19">
         <f>34*10</f>
         <v>340</v>
       </c>
@@ -1674,49 +1673,49 @@
         <f t="shared" si="13"/>
         <v>960</v>
       </c>
-      <c r="D5" s="21">
+      <c r="D5" s="20">
         <v>119</v>
       </c>
-      <c r="E5" s="20">
-        <f t="shared" si="6"/>
+      <c r="E5" s="19">
+        <f t="shared" si="14"/>
         <v>2.9750000000000001</v>
       </c>
-      <c r="F5" s="21">
+      <c r="F5" s="20">
         <f t="shared" si="7"/>
         <v>2.8235294117647061</v>
       </c>
-      <c r="G5" s="20">
+      <c r="G5" s="19">
         <v>968</v>
       </c>
       <c r="H5">
         <f t="shared" si="8"/>
         <v>332</v>
       </c>
-      <c r="I5" s="21">
+      <c r="I5" s="20">
         <v>15</v>
       </c>
-      <c r="J5" s="20">
+      <c r="J5" s="19">
         <f t="shared" si="9"/>
         <v>0.375</v>
       </c>
-      <c r="K5" s="21">
+      <c r="K5" s="20">
         <f t="shared" si="10"/>
         <v>0.34297520661157027</v>
       </c>
-      <c r="L5" s="20">
+      <c r="L5" s="19">
         <f t="shared" si="11"/>
         <v>251.07692307692307</v>
       </c>
-      <c r="M5" s="21">
+      <c r="M5" s="20">
         <f t="shared" si="12"/>
         <v>247.21230769230769</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="14">
+      <c r="A6" s="13">
         <v>1400</v>
       </c>
-      <c r="B6" s="20">
+      <c r="B6" s="19">
         <f>32.9*10</f>
         <v>329</v>
       </c>
@@ -1724,90 +1723,90 @@
         <f t="shared" si="13"/>
         <v>1071</v>
       </c>
-      <c r="D6" s="21">
+      <c r="D6" s="20">
         <v>137</v>
       </c>
-      <c r="E6" s="20">
-        <f t="shared" si="6"/>
+      <c r="E6" s="19">
+        <f t="shared" si="14"/>
         <v>3.4249999999999998</v>
       </c>
-      <c r="F6" s="21">
+      <c r="F6" s="20">
         <f t="shared" si="7"/>
         <v>3.2553191489361701</v>
       </c>
-      <c r="G6" s="20">
+      <c r="G6" s="19">
         <v>1074</v>
       </c>
       <c r="H6">
         <f t="shared" si="8"/>
         <v>326</v>
       </c>
-      <c r="I6" s="21">
+      <c r="I6" s="20">
         <v>13</v>
       </c>
-      <c r="J6" s="20">
+      <c r="J6" s="19">
         <f t="shared" si="9"/>
         <v>0.32500000000000001</v>
       </c>
-      <c r="K6" s="21">
+      <c r="K6" s="20">
         <f t="shared" si="10"/>
         <v>0.30353817504655495</v>
       </c>
-      <c r="L6" s="20">
+      <c r="L6" s="19">
         <f t="shared" si="11"/>
         <v>251.685</v>
       </c>
-      <c r="M6" s="21">
+      <c r="M6" s="20">
         <f t="shared" si="12"/>
         <v>250.08857142857144</v>
       </c>
     </row>
     <row r="7" ht="14.65">
-      <c r="A7" s="14">
+      <c r="A7" s="13">
         <v>1500</v>
       </c>
-      <c r="B7" s="24">
+      <c r="B7" s="23">
         <f>31.9*10</f>
         <v>319</v>
       </c>
-      <c r="C7" s="25">
+      <c r="C7" s="24">
         <f t="shared" si="13"/>
         <v>1181</v>
       </c>
-      <c r="D7" s="26">
+      <c r="D7" s="25">
         <v>155</v>
       </c>
-      <c r="E7" s="24">
-        <f t="shared" si="6"/>
+      <c r="E7" s="23">
+        <f t="shared" si="14"/>
         <v>3.875</v>
       </c>
-      <c r="F7" s="26">
+      <c r="F7" s="25">
         <f t="shared" si="7"/>
         <v>3.7021943573667713</v>
       </c>
-      <c r="G7" s="24">
+      <c r="G7" s="23">
         <v>1186</v>
       </c>
-      <c r="H7" s="25">
+      <c r="H7" s="24">
         <f t="shared" si="8"/>
         <v>314</v>
       </c>
-      <c r="I7" s="26">
+      <c r="I7" s="25">
         <v>12</v>
       </c>
-      <c r="J7" s="24">
+      <c r="J7" s="23">
         <f t="shared" si="9"/>
         <v>0.29999999999999999</v>
       </c>
-      <c r="K7" s="26">
+      <c r="K7" s="25">
         <f t="shared" si="10"/>
         <v>0.26475548060708265</v>
       </c>
-      <c r="L7" s="24">
+      <c r="L7" s="23">
         <f t="shared" si="11"/>
         <v>251.15933333333334</v>
       </c>
-      <c r="M7" s="26">
+      <c r="M7" s="25">
         <f t="shared" si="12"/>
         <v>248.26933333333332</v>
       </c>
@@ -1841,285 +1840,285 @@
   </cols>
   <sheetData>
     <row r="1" ht="14.65">
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="27" t="s">
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="H1" s="28"/>
-      <c r="I1" s="28"/>
-      <c r="J1" s="28"/>
-      <c r="K1" s="29"/>
+      <c r="H1" s="27"/>
+      <c r="I1" s="27"/>
+      <c r="J1" s="27"/>
+      <c r="K1" s="28"/>
     </row>
     <row r="2" ht="16.899999999999999" customHeight="1">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="30" t="s">
+      <c r="B2" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="C2" s="31" t="s">
+      <c r="C2" s="30" t="s">
         <v>27</v>
       </c>
-      <c r="D2" s="32" t="s">
+      <c r="D2" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="E2" s="15" t="s">
+      <c r="E2" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="F2" s="17" t="s">
+      <c r="F2" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="G2" s="30" t="s">
+      <c r="G2" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="H2" s="31" t="s">
+      <c r="H2" s="30" t="s">
         <v>27</v>
       </c>
-      <c r="I2" s="33" t="s">
+      <c r="I2" s="32" t="s">
         <v>37</v>
       </c>
-      <c r="J2" s="15" t="s">
+      <c r="J2" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="K2" s="17" t="s">
+      <c r="K2" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="L2" s="34" t="s">
+      <c r="L2" s="33" t="s">
         <v>31</v>
       </c>
-      <c r="M2" s="17" t="s">
+      <c r="M2" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="N2" s="35" t="s">
+      <c r="N2" s="34" t="s">
         <v>33</v>
       </c>
-      <c r="O2" s="36" t="s">
+      <c r="O2" s="35" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="3" ht="14.65">
-      <c r="A3" s="37">
+      <c r="A3" s="36">
         <v>600</v>
       </c>
-      <c r="B3" s="38">
+      <c r="B3" s="37">
         <v>139</v>
       </c>
-      <c r="C3" s="39">
-        <f t="shared" ref="C3:C6" si="14">A3-B3</f>
+      <c r="C3" s="38">
+        <f t="shared" ref="C3:C6" si="15">A3-B3</f>
         <v>461</v>
       </c>
-      <c r="D3" s="23">
+      <c r="D3" s="22">
         <v>146</v>
       </c>
-      <c r="E3" s="22">
-        <f t="shared" ref="E3:E6" si="15">D3/40</f>
+      <c r="E3" s="21">
+        <f t="shared" ref="E3:E6" si="16">D3/40</f>
         <v>3.6499999999999999</v>
       </c>
-      <c r="F3" s="23">
-        <f t="shared" ref="F3:F6" si="16">C3/B3</f>
+      <c r="F3" s="22">
+        <f t="shared" ref="F3:F6" si="17">C3/B3</f>
         <v>3.3165467625899279</v>
       </c>
-      <c r="G3" s="22">
+      <c r="G3" s="21">
         <v>467</v>
       </c>
-      <c r="H3" s="39">
-        <f t="shared" ref="H3:H6" si="17">A3-G3</f>
+      <c r="H3" s="38">
+        <f t="shared" ref="H3:H6" si="18">A3-G3</f>
         <v>133</v>
       </c>
-      <c r="I3" s="23">
+      <c r="I3" s="22">
         <v>13</v>
       </c>
-      <c r="J3" s="22">
-        <f t="shared" ref="J3:J6" si="18">I3/40</f>
+      <c r="J3" s="21">
+        <f t="shared" ref="J3:J6" si="19">I3/40</f>
         <v>0.32500000000000001</v>
       </c>
-      <c r="K3" s="23">
-        <f t="shared" ref="K3:K6" si="19">H3/G3</f>
+      <c r="K3" s="22">
+        <f t="shared" ref="K3:K6" si="20">H3/G3</f>
         <v>0.28479657387580298</v>
       </c>
-      <c r="L3" s="23">
-        <f t="shared" ref="L3:L6" si="20">(B3*C3)/(B3+C3)</f>
+      <c r="L3" s="22">
+        <f t="shared" ref="L3:L6" si="21">(B3*C3)/(B3+C3)</f>
         <v>106.79833333333333</v>
       </c>
-      <c r="M3" s="40">
-        <f t="shared" ref="M3:M6" si="21">(G3*H3)/(G3+H3)</f>
+      <c r="M3" s="39">
+        <f t="shared" ref="M3:M6" si="22">(G3*H3)/(G3+H3)</f>
         <v>103.51833333333333</v>
       </c>
-      <c r="N3" s="41" t="s">
+      <c r="N3" s="40" t="s">
         <v>38</v>
       </c>
-      <c r="O3" s="41" t="s">
+      <c r="O3" s="40" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="42">
+      <c r="A4" s="41">
         <v>550</v>
       </c>
-      <c r="B4" s="43">
+      <c r="B4" s="42">
         <v>146</v>
       </c>
       <c r="C4">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>404</v>
       </c>
-      <c r="D4" s="21">
+      <c r="D4" s="20">
         <v>120</v>
       </c>
-      <c r="E4" s="20">
+      <c r="E4" s="19">
+        <f t="shared" si="16"/>
+        <v>3</v>
+      </c>
+      <c r="F4" s="20">
+        <f t="shared" si="17"/>
+        <v>2.7671232876712328</v>
+      </c>
+      <c r="G4" s="19">
+        <v>413</v>
+      </c>
+      <c r="H4">
+        <f t="shared" si="18"/>
+        <v>137</v>
+      </c>
+      <c r="I4" s="20">
+        <v>15</v>
+      </c>
+      <c r="J4" s="19">
+        <f t="shared" si="19"/>
+        <v>0.375</v>
+      </c>
+      <c r="K4" s="20">
+        <f t="shared" si="20"/>
+        <v>0.33171912832929784</v>
+      </c>
+      <c r="L4" s="20">
+        <f t="shared" si="21"/>
+        <v>107.24363636363637</v>
+      </c>
+      <c r="M4" s="43">
+        <f t="shared" si="22"/>
+        <v>102.87454545454545</v>
+      </c>
+      <c r="N4" s="44"/>
+      <c r="O4" s="44"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="41">
+        <v>500</v>
+      </c>
+      <c r="B5" s="42">
+        <v>155</v>
+      </c>
+      <c r="C5">
         <f t="shared" si="15"/>
-        <v>3</v>
-      </c>
-      <c r="F4" s="21">
+        <v>345</v>
+      </c>
+      <c r="D5" s="20">
+        <v>98</v>
+      </c>
+      <c r="E5" s="19">
         <f t="shared" si="16"/>
-        <v>2.7671232876712328</v>
-      </c>
-      <c r="G4" s="20">
-        <v>413</v>
-      </c>
-      <c r="H4">
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="F5" s="20">
         <f t="shared" si="17"/>
-        <v>137</v>
-      </c>
-      <c r="I4" s="21">
-        <v>15</v>
-      </c>
-      <c r="J4" s="20">
+        <v>2.225806451612903</v>
+      </c>
+      <c r="G5" s="19">
+        <v>355</v>
+      </c>
+      <c r="H5">
         <f t="shared" si="18"/>
-        <v>0.375</v>
-      </c>
-      <c r="K4" s="21">
+        <v>145</v>
+      </c>
+      <c r="I5" s="20">
+        <v>19</v>
+      </c>
+      <c r="J5" s="19">
         <f t="shared" si="19"/>
-        <v>0.33171912832929784</v>
-      </c>
-      <c r="L4" s="21">
+        <v>0.47499999999999998</v>
+      </c>
+      <c r="K5" s="20">
         <f t="shared" si="20"/>
-        <v>107.24363636363637</v>
-      </c>
-      <c r="M4" s="44">
+        <v>0.40845070422535212</v>
+      </c>
+      <c r="L5" s="20">
         <f t="shared" si="21"/>
-        <v>102.87454545454545</v>
-      </c>
-      <c r="N4" s="45"/>
-      <c r="O4" s="45"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="42">
-        <v>500</v>
-      </c>
-      <c r="B5" s="43">
-        <v>155</v>
-      </c>
-      <c r="C5">
-        <f t="shared" si="14"/>
-        <v>345</v>
-      </c>
-      <c r="D5" s="21">
-        <v>98</v>
-      </c>
-      <c r="E5" s="20">
+        <v>106.95</v>
+      </c>
+      <c r="M5" s="43">
+        <f t="shared" si="22"/>
+        <v>102.95</v>
+      </c>
+      <c r="N5" s="44"/>
+      <c r="O5" s="44"/>
+    </row>
+    <row r="6" ht="14.65">
+      <c r="A6" s="45">
+        <v>450</v>
+      </c>
+      <c r="B6" s="46">
+        <v>173</v>
+      </c>
+      <c r="C6" s="24">
         <f t="shared" si="15"/>
-        <v>2.4500000000000002</v>
-      </c>
-      <c r="F5" s="21">
+        <v>277</v>
+      </c>
+      <c r="D6" s="25">
+        <v>68</v>
+      </c>
+      <c r="E6" s="23">
         <f t="shared" si="16"/>
-        <v>2.225806451612903</v>
-      </c>
-      <c r="G5" s="20">
-        <v>355</v>
-      </c>
-      <c r="H5">
+        <v>1.7</v>
+      </c>
+      <c r="F6" s="25">
         <f t="shared" si="17"/>
-        <v>145</v>
-      </c>
-      <c r="I5" s="21">
-        <v>19</v>
-      </c>
-      <c r="J5" s="20">
+        <v>1.6011560693641618</v>
+      </c>
+      <c r="G6" s="23">
+        <v>285</v>
+      </c>
+      <c r="H6" s="24">
         <f t="shared" si="18"/>
-        <v>0.47499999999999998</v>
-      </c>
-      <c r="K5" s="21">
+        <v>165</v>
+      </c>
+      <c r="I6" s="25">
+        <v>26</v>
+      </c>
+      <c r="J6" s="23">
         <f t="shared" si="19"/>
-        <v>0.40845070422535212</v>
-      </c>
-      <c r="L5" s="21">
+        <v>0.65000000000000002</v>
+      </c>
+      <c r="K6" s="25">
         <f t="shared" si="20"/>
-        <v>106.95</v>
-      </c>
-      <c r="M5" s="44">
+        <v>0.57894736842105265</v>
+      </c>
+      <c r="L6" s="25">
         <f t="shared" si="21"/>
-        <v>102.95</v>
-      </c>
-      <c r="N5" s="45"/>
-      <c r="O5" s="45"/>
-    </row>
-    <row r="6" ht="14.65">
-      <c r="A6" s="46">
-        <v>450</v>
-      </c>
-      <c r="B6" s="47">
-        <v>173</v>
-      </c>
-      <c r="C6" s="25">
-        <f t="shared" si="14"/>
-        <v>277</v>
-      </c>
-      <c r="D6" s="26">
-        <v>68</v>
-      </c>
-      <c r="E6" s="24">
-        <f t="shared" si="15"/>
-        <v>1.7</v>
-      </c>
-      <c r="F6" s="26">
-        <f t="shared" si="16"/>
-        <v>1.6011560693641618</v>
-      </c>
-      <c r="G6" s="24">
-        <v>285</v>
-      </c>
-      <c r="H6" s="25">
-        <f t="shared" si="17"/>
-        <v>165</v>
-      </c>
-      <c r="I6" s="26">
-        <v>26</v>
-      </c>
-      <c r="J6" s="24">
-        <f t="shared" si="18"/>
-        <v>0.65000000000000002</v>
-      </c>
-      <c r="K6" s="26">
-        <f t="shared" si="19"/>
-        <v>0.57894736842105265</v>
-      </c>
-      <c r="L6" s="26">
-        <f t="shared" si="20"/>
         <v>106.49111111111111</v>
       </c>
-      <c r="M6" s="48">
-        <f t="shared" si="21"/>
+      <c r="M6" s="47">
+        <f t="shared" si="22"/>
         <v>104.5</v>
       </c>
-      <c r="N6" s="45"/>
-      <c r="O6" s="45"/>
+      <c r="N6" s="44"/>
+      <c r="O6" s="44"/>
     </row>
     <row r="7">
-      <c r="C7" s="45"/>
-      <c r="D7" s="45"/>
+      <c r="C7" s="44"/>
+      <c r="D7" s="44"/>
     </row>
     <row r="8">
       <c r="D8" s="5"/>
     </row>
     <row r="9">
-      <c r="C9" s="45"/>
+      <c r="C9" s="44"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/Banco ottico.xlsx
+++ b/Banco ottico.xlsx
@@ -1,60 +1,77 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimibit-my.sharepoint.com/personal/m_declich_campus_unimib_it/Documents/Documenti/Università/I° anno/Laboratorio I/Esperienze in laboratorio/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="99" documentId="11_2BDBA90D71226A740C9D53B8AF822B342D3B3C81" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CD78A13D-9B4E-49A4-8FBD-4142FDDA0BBD}"/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="2"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Angoli di rifrazione" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Distanze" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Distanze focali (250mm)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Distanze focali (100mm)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Angoli di rifrazione" sheetId="1" r:id="rId1"/>
+    <sheet name="Distanze" sheetId="2" r:id="rId2"/>
+    <sheet name="Distanze focali (250mm)" sheetId="3" r:id="rId3"/>
+    <sheet name="Distanze focali (100mm)" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{D0CA8CA8-9F24-4464-BF8E-62219DCF47F9}"/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
-  <si>
-    <t xml:space="preserve">Lato piatto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lato curvo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">θ inc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sinθ inc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">θ rif</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sinθ rif</t>
-  </si>
-  <si>
-    <t xml:space="preserve">θ critico</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="40">
+  <si>
+    <t>Lato piatto</t>
+  </si>
+  <si>
+    <t>Lato curvo</t>
+  </si>
+  <si>
+    <t>θ inc</t>
+  </si>
+  <si>
+    <t>sinθ inc</t>
+  </si>
+  <si>
+    <t>θ rif</t>
+  </si>
+  <si>
+    <t>sinθ rif</t>
+  </si>
+  <si>
+    <t>θ critico</t>
   </si>
   <si>
     <t>Reversibilità</t>
   </si>
   <si>
-    <t xml:space="preserve">θ' inc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">θ' rif</t>
-  </si>
-  <si>
-    <t xml:space="preserve">δ minimo (rad)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">α (rad)</t>
+    <t>θ' inc</t>
+  </si>
+  <si>
+    <t>θ' rif</t>
+  </si>
+  <si>
+    <t>δ minimo (rad)</t>
+  </si>
+  <si>
+    <t>α (rad)</t>
   </si>
   <si>
     <t>n</t>
@@ -63,25 +80,25 @@
     <t>σn</t>
   </si>
   <si>
-    <t xml:space="preserve">prisma a base triangolare</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prisma a base trapezioidale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">h prisma trapezoidale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32mm (1mm)</t>
+    <t>prisma a base triangolare</t>
+  </si>
+  <si>
+    <t>prisma a base trapezioidale</t>
+  </si>
+  <si>
+    <t>h prisma trapezoidale</t>
+  </si>
+  <si>
+    <t>32mm (1mm)</t>
   </si>
   <si>
     <t>ANGOLI</t>
   </si>
   <si>
-    <t xml:space="preserve">Distanza dal centro [mm]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Distanza attesa [mm]</t>
+    <t>Distanza dal centro [mm]</t>
+  </si>
+  <si>
+    <t>Distanza attesa [mm]</t>
   </si>
   <si>
     <t>Seno</t>
@@ -90,74 +107,76 @@
     <t>Coseno</t>
   </si>
   <si>
-    <t xml:space="preserve">Fuoco 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fuoco 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D totale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p (mm)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">q (mm)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">h' (mm)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M misurato</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M atteso</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DISTANZA FOCALE 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DISTANZA FOCALE 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D. MINIMA OSS.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D. MINIMA TEOR.</t>
+    <t>Fuoco 1</t>
+  </si>
+  <si>
+    <t>Fuoco 2</t>
+  </si>
+  <si>
+    <t>D totale</t>
+  </si>
+  <si>
+    <t>p (mm)</t>
+  </si>
+  <si>
+    <t>q (mm)</t>
+  </si>
+  <si>
+    <t>h' (mm)</t>
+  </si>
+  <si>
+    <t>M misurato</t>
+  </si>
+  <si>
+    <t>M atteso</t>
+  </si>
+  <si>
+    <t>DISTANZA FOCALE 1</t>
+  </si>
+  <si>
+    <t>DISTANZA FOCALE 2</t>
+  </si>
+  <si>
+    <t>D. MINIMA OSS.</t>
+  </si>
+  <si>
+    <t>D. MINIMA TEOR.</t>
   </si>
   <si>
     <t>999mm</t>
   </si>
   <si>
-    <t xml:space="preserve">1000 mm</t>
+    <t>1000 mm</t>
   </si>
   <si>
     <t>h'</t>
   </si>
   <si>
-    <t xml:space="preserve">405 mm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">400 mm</t>
+    <t>405 mm</t>
+  </si>
+  <si>
+    <t>400 mm</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="0.0000"/>
+    <numFmt numFmtId="166" formatCode="0.000"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <sz val="11.000000"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
     <font>
       <u/>
-      <sz val="11.000000"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
@@ -195,6 +214,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
@@ -210,56 +230,56 @@
   </fills>
   <borders count="16">
     <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="medium">
         <color auto="1"/>
       </left>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
-      <left style="none"/>
+      <left/>
       <right style="medium">
         <color auto="1"/>
       </right>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="medium">
         <color auto="1"/>
       </left>
-      <right style="none"/>
+      <right/>
       <top style="medium">
         <color auto="1"/>
       </top>
       <bottom style="medium">
         <color auto="1"/>
       </bottom>
-      <diagonal style="none"/>
+      <diagonal/>
     </border>
     <border>
-      <left style="none"/>
-      <right style="none"/>
+      <left/>
+      <right/>
       <top style="medium">
         <color auto="1"/>
       </top>
       <bottom style="medium">
         <color auto="1"/>
       </bottom>
-      <diagonal style="none"/>
+      <diagonal/>
     </border>
     <border>
-      <left style="none"/>
+      <left/>
       <right style="medium">
         <color auto="1"/>
       </right>
@@ -269,69 +289,69 @@
       <bottom style="medium">
         <color auto="1"/>
       </bottom>
-      <diagonal style="none"/>
+      <diagonal/>
     </border>
     <border>
       <left style="medium">
         <color auto="1"/>
       </left>
-      <right style="none"/>
+      <right/>
       <top style="medium">
         <color auto="1"/>
       </top>
-      <bottom style="none"/>
-      <diagonal style="none"/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
-      <left style="none"/>
+      <left/>
       <right style="medium">
         <color auto="1"/>
       </right>
       <top style="medium">
         <color auto="1"/>
       </top>
-      <bottom style="none"/>
-      <diagonal style="none"/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="medium">
         <color auto="1"/>
       </left>
-      <right style="none"/>
-      <top style="none"/>
+      <right/>
+      <top/>
       <bottom style="medium">
         <color auto="1"/>
       </bottom>
-      <diagonal style="none"/>
+      <diagonal/>
     </border>
     <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="medium">
         <color auto="1"/>
       </bottom>
-      <diagonal style="none"/>
+      <diagonal/>
     </border>
     <border>
-      <left style="none"/>
+      <left/>
       <right style="medium">
         <color auto="1"/>
       </right>
-      <top style="none"/>
+      <top/>
       <bottom style="medium">
         <color auto="1"/>
       </bottom>
-      <diagonal style="none"/>
+      <diagonal/>
     </border>
     <border>
-      <left style="none"/>
-      <right style="none"/>
+      <left/>
+      <right/>
       <top style="medium">
         <color auto="1"/>
       </top>
-      <bottom style="none"/>
-      <diagonal style="none"/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="medium">
@@ -346,7 +366,7 @@
       <bottom style="medium">
         <color auto="1"/>
       </bottom>
-      <diagonal style="none"/>
+      <diagonal/>
     </border>
     <border>
       <left style="medium">
@@ -358,8 +378,8 @@
       <top style="medium">
         <color auto="1"/>
       </top>
-      <bottom style="none"/>
-      <diagonal style="none"/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="medium">
@@ -368,9 +388,9 @@
       <right style="medium">
         <color auto="1"/>
       </right>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="medium">
@@ -379,89 +399,102 @@
       <right style="medium">
         <color auto="1"/>
       </right>
-      <top style="none"/>
+      <top/>
       <bottom style="medium">
         <color auto="1"/>
       </bottom>
-      <diagonal style="none"/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
-    <xf fontId="0" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyAlignment="1">
+  <cellXfs count="63">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="0" fillId="3" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="1" xfId="0" applyNumberFormat="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
-      <protection hidden="0" locked="1"/>
-    </xf>
-    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf fontId="0" fillId="4" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
-    <xf fontId="0" fillId="5" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" quotePrefix="1"/>
-    <xf fontId="0" fillId="6" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
-    <xf fontId="0" fillId="4" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="0" fillId="4" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="0" fillId="4" borderId="2" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="0" fillId="7" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
-    <xf fontId="0" fillId="8" borderId="3" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="8" borderId="4" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="8" borderId="5" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="8" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf fontId="0" fillId="8" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="2" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="6" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="7" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="8" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="9" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="10" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="4" borderId="3" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="0" fillId="4" borderId="4" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="0" fillId="4" borderId="5" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="0" fillId="8" borderId="6" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="8" borderId="11" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="8" borderId="7" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="8" borderId="2" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="8" borderId="12" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="8" borderId="12" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf fontId="0" fillId="8" borderId="5" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="0" fillId="7" borderId="13" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="11" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="11" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="13" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="5" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="7" borderId="14" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1"/>
-    <xf fontId="0" fillId="0" borderId="14" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
-    <xf fontId="0" fillId="7" borderId="15" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="9" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="15" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -479,291 +512,8 @@
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
-  <a:themeElements>
-    <a:clrScheme name="Office">
-      <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="1F497D"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="EEECE1"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="4F81BD"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="C0504D"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="9BBB59"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="8064A2"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="4BACC6"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="F79646"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="0000FF"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="800080"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Office">
-      <a:majorFont>
-        <a:latin typeface="Cambria"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Angsana New"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ 明朝"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Cordia New"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme name="Office">
-      <a:fillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="35000">
-              <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
-        </a:gradFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
-        </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="40000">
-              <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
-        </a:gradFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-</a:theme>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" name="Tema di Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema di Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -974,74 +724,76 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="14.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:I16"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col bestFit="1" customWidth="1" min="1" max="1" width="4.453125"/>
-    <col bestFit="1" customWidth="1" min="2" max="2" width="11.125"/>
-    <col bestFit="1" min="3" max="3" width="4.79296875"/>
-    <col bestFit="1" min="4" max="4" width="11.125"/>
-    <col bestFit="1" min="5" max="5" width="4.79296875"/>
-    <col bestFit="1" min="6" max="6" width="11.125"/>
-    <col bestFit="1" min="7" max="7" width="6.875"/>
+    <col min="1" max="1" width="4.46484375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.1328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.796875" bestFit="1"/>
+    <col min="4" max="4" width="11.1328125" bestFit="1"/>
+    <col min="5" max="5" width="4.796875" bestFit="1"/>
+    <col min="6" max="6" width="11.1328125" bestFit="1"/>
+    <col min="7" max="7" width="6.86328125" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="C1" s="1" t="s">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="C1" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1" t="s">
+      <c r="D1" s="38"/>
+      <c r="E1" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="1"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="s">
+      <c r="F1" s="38"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A3" s="2">
         <v>20</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="57">
         <f t="shared" ref="B3:B8" si="0">SIN((A3*PI())/180)</f>
         <v>0.34202014332566871</v>
       </c>
       <c r="C3">
         <v>13</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="57">
         <f t="shared" ref="D3:D8" si="1">SIN((C3*PI())/180)</f>
         <v>0.224951054343865</v>
       </c>
       <c r="E3">
         <v>30</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="57">
         <f t="shared" ref="F3:F8" si="2">SIN((E3*PI())/180)</f>
         <v>0.49999999999999994</v>
       </c>
@@ -1049,221 +801,221 @@
         <v>44</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A4">
         <v>25</v>
       </c>
-      <c r="B4" s="4">
+      <c r="B4" s="57">
         <f t="shared" si="0"/>
         <v>0.42261826174069944</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4">
         <v>16</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4" s="57">
         <f t="shared" si="1"/>
         <v>0.27563735581699916</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E4">
         <v>39</v>
       </c>
-      <c r="F4" s="4">
+      <c r="F4" s="57">
         <f t="shared" si="2"/>
         <v>0.62932039104983739</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A5">
         <v>30</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="57">
         <f t="shared" si="0"/>
         <v>0.49999999999999994</v>
       </c>
       <c r="C5">
         <v>20</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="57">
         <f t="shared" si="1"/>
         <v>0.34202014332566871</v>
       </c>
       <c r="E5">
         <v>48</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="57">
         <f t="shared" si="2"/>
-        <v>0.74314482547739424</v>
-      </c>
-    </row>
-    <row r="6">
+        <v>0.74314482547739413</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A6">
         <v>45</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="57">
         <f t="shared" si="0"/>
         <v>0.70710678118654746</v>
       </c>
       <c r="C6">
         <v>28</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="57">
         <f t="shared" si="1"/>
         <v>0.46947156278589081</v>
       </c>
       <c r="E6">
         <v>136</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="57">
         <f t="shared" si="2"/>
         <v>0.69465837045899714</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A7">
         <v>60</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="57">
         <f t="shared" si="0"/>
         <v>0.8660254037844386</v>
       </c>
       <c r="C7">
         <v>35</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="57">
         <f t="shared" si="1"/>
         <v>0.57357643635104605</v>
       </c>
       <c r="E7">
         <v>120</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="57">
         <f t="shared" si="2"/>
         <v>0.86602540378443871</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A8">
         <v>70</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="57">
         <f t="shared" si="0"/>
         <v>0.93969262078590832</v>
       </c>
       <c r="C8">
         <v>39</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="57">
         <f t="shared" si="1"/>
         <v>0.62932039104983739</v>
       </c>
       <c r="E8">
         <v>111</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="57">
         <f t="shared" si="2"/>
         <v>0.93358042649720174</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="1" t="s">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A10" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="1"/>
-      <c r="C10" s="2" t="s">
+      <c r="B10" s="38"/>
+      <c r="C10" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E10" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="F10" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="I10" s="5"/>
-    </row>
-    <row r="11" ht="14.25">
+      <c r="I10" s="3"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.45">
       <c r="C11">
         <v>13</v>
       </c>
-      <c r="D11" s="4">
+      <c r="D11">
         <v>19</v>
       </c>
-      <c r="E11" s="4">
+      <c r="E11">
         <v>30</v>
       </c>
-      <c r="F11" s="4">
+      <c r="F11">
         <v>20</v>
       </c>
     </row>
-    <row r="12" ht="14.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.45">
       <c r="C12">
         <v>16</v>
       </c>
-      <c r="D12" s="4">
+      <c r="D12">
         <v>24</v>
       </c>
-      <c r="E12" s="4">
+      <c r="E12">
         <v>25</v>
       </c>
-      <c r="F12" s="4">
+      <c r="F12">
         <v>25</v>
       </c>
     </row>
-    <row r="13" ht="14.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.45">
       <c r="C13">
         <v>20</v>
       </c>
-      <c r="D13" s="4">
+      <c r="D13">
         <v>30</v>
       </c>
-      <c r="E13" s="4">
+      <c r="E13">
         <v>48</v>
       </c>
-      <c r="F13" s="4">
+      <c r="F13">
         <v>30</v>
       </c>
     </row>
-    <row r="14" ht="14.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.45">
       <c r="C14">
         <v>28</v>
       </c>
-      <c r="D14" s="4">
+      <c r="D14">
         <v>44</v>
       </c>
-      <c r="E14" s="4">
+      <c r="E14">
         <v>136</v>
       </c>
-      <c r="F14" s="4">
+      <c r="F14">
         <v>45</v>
       </c>
     </row>
-    <row r="15" ht="14.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.45">
       <c r="C15">
         <v>35</v>
       </c>
-      <c r="D15" s="4">
+      <c r="D15">
         <v>57</v>
       </c>
-      <c r="E15" s="4">
+      <c r="E15">
         <v>121</v>
       </c>
-      <c r="F15" s="4">
+      <c r="F15">
         <v>58</v>
       </c>
     </row>
-    <row r="16" ht="14.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.45">
       <c r="C16">
         <v>39</v>
       </c>
-      <c r="D16" s="4">
+      <c r="D16">
         <v>68</v>
       </c>
-      <c r="E16" s="4">
+      <c r="E16">
         <v>111</v>
       </c>
-      <c r="F16" s="4">
+      <c r="F16">
         <v>69</v>
       </c>
     </row>
@@ -1273,95 +1025,95 @@
     <mergeCell ref="E1:F1"/>
     <mergeCell ref="A10:B10"/>
   </mergeCells>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="14.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:E12"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="23.46484375"/>
-    <col bestFit="1" customWidth="1" min="2" max="2" width="20.625"/>
-    <col bestFit="1" customWidth="1" min="3" max="3" width="17.625"/>
-    <col bestFit="1" customWidth="1" min="4" max="4" width="12.33203125"/>
+    <col min="1" max="1" width="23.46484375" customWidth="1"/>
+    <col min="2" max="2" width="20.59765625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.59765625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.3984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="B1" s="6" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="B1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="5" t="s">
         <v>12</v>
       </c>
       <c r="E1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="6" t="s">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A2" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="58">
         <f>PI()/4</f>
         <v>0.78539816339744828</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="58">
         <f>PI()/3</f>
         <v>1.0471975511965976</v>
       </c>
-      <c r="D2">
-        <f t="shared" ref="D2:D3" si="3">(SIN((B2/2)+(C2/2))/(SIN(C2/2)))</f>
+      <c r="D2" s="58">
+        <f t="shared" ref="D2:D3" si="0">(SIN((B2/2)+(C2/2))/(SIN(C2/2)))</f>
         <v>1.5867066805824706</v>
       </c>
-      <c r="E2" s="8">
-        <f t="shared" ref="E2:E3" si="4">((1/(2*SIN(C2/2)))*COS(((PI()/180)+C2)/2))*((PI()/180))</f>
-        <v>1.5038265780899108e-002</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="6" t="s">
+      <c r="E2" s="56">
+        <f t="shared" ref="E2:E3" si="1">((1/(2*SIN(C2/2)))*COS(((PI()/180)+C2)/2))*((PI()/180))</f>
+        <v>1.5038265780899104E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A3" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="58">
         <f>(27*PI())/180</f>
         <v>0.47123889803846897</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="58">
         <f>PI()/4</f>
         <v>0.78539816339744828</v>
       </c>
-      <c r="D3">
-        <f t="shared" si="3"/>
+      <c r="D3" s="58">
+        <f t="shared" si="0"/>
         <v>1.5359568838917252</v>
       </c>
-      <c r="E3" s="8">
-        <f t="shared" si="4"/>
-        <v>2.0991032162068827e-002</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="9" t="s">
+      <c r="E3" s="56">
+        <f t="shared" si="1"/>
+        <v>2.0991032162068827E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A5" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="6" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="6" t="s">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A7" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="4" t="s">
         <v>20</v>
       </c>
       <c r="D7" t="s">
@@ -1371,237 +1123,236 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="6">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A8" s="4">
         <v>10</v>
       </c>
       <c r="B8">
         <v>2</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="58">
         <f>32*D8*(1-(E8/SQRT(D3^2-D8^2)))</f>
         <v>1.9709421734493859</v>
       </c>
-      <c r="D8">
-        <f t="shared" ref="D8:D12" si="5">SIN((A8*PI())/180)</f>
+      <c r="D8" s="57">
+        <f t="shared" ref="D8:D12" si="2">SIN((A8*PI())/180)</f>
         <v>0.17364817766693033</v>
       </c>
-      <c r="E8">
-        <f t="shared" ref="E8:E12" si="6">COS((A8*PI())/180)</f>
+      <c r="E8" s="57">
+        <f t="shared" ref="E8:E12" si="3">COS((A8*PI())/180)</f>
         <v>0.98480775301220802</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="6">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A9" s="4">
         <v>20</v>
       </c>
       <c r="B9">
         <v>4</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="58">
         <f>32*D9*(1-(E9/SQRT(D3^2-D9^2)))</f>
         <v>4.0763062050074748</v>
       </c>
-      <c r="D9">
-        <f t="shared" si="5"/>
+      <c r="D9" s="57">
+        <f t="shared" si="2"/>
         <v>0.34202014332566871</v>
       </c>
-      <c r="E9">
-        <f t="shared" si="6"/>
+      <c r="E9" s="57">
+        <f t="shared" si="3"/>
         <v>0.93969262078590843</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="6">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A10" s="4">
         <v>30</v>
       </c>
       <c r="B10">
         <v>6</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="58">
         <f>32*D10*(1-(E10/SQRT(D3^2-D10^2)))</f>
         <v>6.4589650713431856</v>
       </c>
-      <c r="D10">
-        <f t="shared" si="5"/>
+      <c r="D10" s="57">
+        <f t="shared" si="2"/>
         <v>0.49999999999999994</v>
       </c>
-      <c r="E10">
-        <f t="shared" si="6"/>
+      <c r="E10" s="57">
+        <f t="shared" si="3"/>
         <v>0.86602540378443871</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="6">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A11" s="4">
         <v>40</v>
       </c>
       <c r="B11">
         <v>9</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="58">
         <f>32*D11*(1-(E11/SQRT(D3^2-D11^2)))</f>
         <v>9.2738090225061391</v>
       </c>
-      <c r="D11">
-        <f t="shared" si="5"/>
+      <c r="D11" s="57">
+        <f t="shared" si="2"/>
         <v>0.64278760968653925</v>
       </c>
-      <c r="E11">
-        <f t="shared" si="6"/>
+      <c r="E11" s="57">
+        <f t="shared" si="3"/>
         <v>0.76604444311897801</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="6">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A12" s="4">
         <v>50</v>
       </c>
       <c r="B12">
         <v>12</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="58">
         <f>32*D12*(1-(E12/SQRT(D3^2-D12^2)))</f>
         <v>12.677612089302682</v>
       </c>
-      <c r="D12">
-        <f t="shared" si="5"/>
+      <c r="D12" s="57">
+        <f t="shared" si="2"/>
         <v>0.76604444311897801</v>
       </c>
-      <c r="E12">
-        <f t="shared" si="6"/>
+      <c r="E12" s="57">
+        <f t="shared" si="3"/>
         <v>0.64278760968653936</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="14.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:O13"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col customWidth="1" min="8" max="8" width="10.19921875"/>
-    <col customWidth="1" min="9" max="9" width="10.9296875"/>
-    <col customWidth="1" min="10" max="10" width="13.9296875"/>
-    <col customWidth="1" min="11" max="11" width="14.9296875"/>
-    <col customWidth="1" min="12" max="12" width="16.9296875"/>
-    <col customWidth="1" min="13" max="13" width="16.86328125"/>
-    <col customWidth="1" min="14" max="14" width="17"/>
-    <col customWidth="1" min="15" max="15" width="15"/>
+    <col min="8" max="8" width="10.19921875" customWidth="1"/>
+    <col min="9" max="9" width="10.9296875" customWidth="1"/>
+    <col min="10" max="10" width="13.9296875" customWidth="1"/>
+    <col min="11" max="11" width="14.9296875" customWidth="1"/>
+    <col min="12" max="12" width="16.9296875" customWidth="1"/>
+    <col min="13" max="13" width="16.86328125" customWidth="1"/>
+    <col min="14" max="14" width="17" customWidth="1"/>
+    <col min="15" max="15" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.65">
-      <c r="B1" s="10" t="s">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="B1" s="35" t="s">
         <v>23</v>
       </c>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="10" t="s">
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="35" t="s">
         <v>24</v>
       </c>
-      <c r="H1" s="11"/>
-      <c r="I1" s="11"/>
-      <c r="J1" s="11"/>
-      <c r="K1" s="11"/>
-    </row>
-    <row r="2" ht="28.5">
-      <c r="A2" s="13" t="s">
+      <c r="H1" s="36"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A2" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="C2" s="15" t="s">
+      <c r="C2" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="D2" s="16" t="s">
+      <c r="D2" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="E2" s="15" t="s">
+      <c r="E2" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="F2" s="15" t="s">
+      <c r="F2" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="G2" s="14" t="s">
+      <c r="G2" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="H2" s="15" t="s">
+      <c r="H2" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="I2" s="16" t="s">
+      <c r="I2" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="J2" s="15" t="s">
+      <c r="J2" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="K2" s="15" t="s">
+      <c r="K2" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="L2" s="14" t="s">
+      <c r="L2" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="M2" s="16" t="s">
+      <c r="M2" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="N2" s="17" t="s">
+      <c r="N2" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="O2" s="18" t="s">
+      <c r="O2" s="12" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="13">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A3" s="7">
         <v>1100</v>
       </c>
-      <c r="B3" s="19">
+      <c r="B3" s="13">
         <f>39*10</f>
         <v>390</v>
       </c>
       <c r="C3">
         <v>710</v>
       </c>
-      <c r="D3" s="20">
+      <c r="D3" s="14">
         <v>77</v>
       </c>
-      <c r="E3" s="19">
+      <c r="E3" s="42">
         <f>D3/40</f>
         <v>1.925</v>
       </c>
-      <c r="F3" s="20">
-        <f t="shared" ref="F3:F7" si="7">C3/B3</f>
+      <c r="F3" s="44">
+        <f t="shared" ref="F3:F7" si="0">C3/B3</f>
         <v>1.8205128205128205</v>
       </c>
-      <c r="G3" s="19">
+      <c r="G3" s="13">
         <v>720</v>
       </c>
       <c r="H3">
-        <f t="shared" ref="H3:H7" si="8">A3-G3</f>
+        <f t="shared" ref="H3:H7" si="1">A3-G3</f>
         <v>380</v>
       </c>
-      <c r="I3" s="20">
+      <c r="I3" s="14">
         <v>22</v>
       </c>
-      <c r="J3" s="21">
-        <f t="shared" ref="J3:J7" si="9">I3/40</f>
+      <c r="J3" s="48">
+        <f t="shared" ref="J3:J7" si="2">I3/40</f>
         <v>0.55000000000000004</v>
       </c>
-      <c r="K3" s="22">
-        <f t="shared" ref="K3:K7" si="10">H3/G3</f>
+      <c r="K3" s="51">
+        <f t="shared" ref="K3:K7" si="3">H3/G3</f>
         <v>0.52777777777777779</v>
       </c>
-      <c r="L3" s="19">
-        <f t="shared" ref="L3:L7" si="11">(B3*C3)/(B3+C3)</f>
+      <c r="L3" s="46">
+        <f t="shared" ref="L3:L7" si="4">(B3*C3)/(B3+C3)</f>
         <v>251.72727272727272</v>
       </c>
-      <c r="M3" s="20">
-        <f t="shared" ref="M3:M7" si="12">(G3*H3)/(G3+H3)</f>
+      <c r="M3" s="54">
+        <f t="shared" ref="M3:M7" si="5">(G3*H3)/(G3+H3)</f>
         <v>248.72727272727272</v>
       </c>
       <c r="N3" t="s">
@@ -1611,523 +1362,507 @@
         <v>36</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="13">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A4" s="7">
         <v>1200</v>
       </c>
-      <c r="B4" s="19">
+      <c r="B4" s="13">
         <f>35.5*10</f>
         <v>355</v>
       </c>
       <c r="C4">
-        <f t="shared" ref="C4:C7" si="13">A4-B4</f>
+        <f t="shared" ref="C4:C7" si="6">A4-B4</f>
         <v>845</v>
       </c>
-      <c r="D4" s="20">
+      <c r="D4" s="14">
         <v>100</v>
       </c>
-      <c r="E4" s="19">
-        <f t="shared" ref="E4:E7" si="14">D4/40</f>
+      <c r="E4" s="42">
+        <f t="shared" ref="E4:E7" si="7">D4/40</f>
         <v>2.5</v>
       </c>
-      <c r="F4" s="20">
-        <f t="shared" si="7"/>
+      <c r="F4" s="44">
+        <f t="shared" si="0"/>
         <v>2.380281690140845</v>
       </c>
-      <c r="G4" s="19">
+      <c r="G4" s="13">
         <v>850</v>
       </c>
       <c r="H4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="1"/>
         <v>350</v>
       </c>
-      <c r="I4" s="20">
+      <c r="I4" s="14">
         <v>18</v>
       </c>
-      <c r="J4" s="19">
-        <f t="shared" si="9"/>
-        <v>0.45000000000000001</v>
-      </c>
-      <c r="K4" s="20">
-        <f t="shared" si="10"/>
+      <c r="J4" s="49">
+        <f t="shared" si="2"/>
+        <v>0.45</v>
+      </c>
+      <c r="K4" s="52">
+        <f t="shared" si="3"/>
         <v>0.41176470588235292</v>
       </c>
-      <c r="L4" s="19">
-        <f t="shared" si="11"/>
+      <c r="L4" s="46">
+        <f t="shared" si="4"/>
         <v>249.97916666666666</v>
       </c>
-      <c r="M4" s="20">
-        <f t="shared" si="12"/>
+      <c r="M4" s="54">
+        <f t="shared" si="5"/>
         <v>247.91666666666666</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="13">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A5" s="7">
         <v>1300</v>
       </c>
-      <c r="B5" s="19">
+      <c r="B5" s="13">
         <f>34*10</f>
         <v>340</v>
       </c>
       <c r="C5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="6"/>
         <v>960</v>
       </c>
-      <c r="D5" s="20">
+      <c r="D5" s="14">
         <v>119</v>
       </c>
-      <c r="E5" s="19">
-        <f t="shared" si="14"/>
+      <c r="E5" s="42">
+        <f t="shared" si="7"/>
         <v>2.9750000000000001</v>
       </c>
-      <c r="F5" s="20">
-        <f t="shared" si="7"/>
+      <c r="F5" s="44">
+        <f t="shared" si="0"/>
         <v>2.8235294117647061</v>
       </c>
-      <c r="G5" s="19">
+      <c r="G5" s="13">
         <v>968</v>
       </c>
       <c r="H5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="1"/>
         <v>332</v>
       </c>
-      <c r="I5" s="20">
+      <c r="I5" s="14">
         <v>15</v>
       </c>
-      <c r="J5" s="19">
-        <f t="shared" si="9"/>
+      <c r="J5" s="49">
+        <f t="shared" si="2"/>
         <v>0.375</v>
       </c>
-      <c r="K5" s="20">
-        <f t="shared" si="10"/>
+      <c r="K5" s="52">
+        <f t="shared" si="3"/>
         <v>0.34297520661157027</v>
       </c>
-      <c r="L5" s="19">
-        <f t="shared" si="11"/>
+      <c r="L5" s="46">
+        <f t="shared" si="4"/>
         <v>251.07692307692307</v>
       </c>
-      <c r="M5" s="20">
-        <f t="shared" si="12"/>
+      <c r="M5" s="54">
+        <f t="shared" si="5"/>
         <v>247.21230769230769</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="13">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A6" s="7">
         <v>1400</v>
       </c>
-      <c r="B6" s="19">
+      <c r="B6" s="13">
         <f>32.9*10</f>
         <v>329</v>
       </c>
       <c r="C6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="6"/>
         <v>1071</v>
       </c>
-      <c r="D6" s="20">
+      <c r="D6" s="14">
         <v>137</v>
       </c>
-      <c r="E6" s="19">
-        <f t="shared" si="14"/>
+      <c r="E6" s="42">
+        <f t="shared" si="7"/>
         <v>3.4249999999999998</v>
       </c>
-      <c r="F6" s="20">
-        <f t="shared" si="7"/>
+      <c r="F6" s="44">
+        <f t="shared" si="0"/>
         <v>3.2553191489361701</v>
       </c>
-      <c r="G6" s="19">
+      <c r="G6" s="13">
         <v>1074</v>
       </c>
       <c r="H6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="1"/>
         <v>326</v>
       </c>
-      <c r="I6" s="20">
+      <c r="I6" s="14">
         <v>13</v>
       </c>
-      <c r="J6" s="19">
-        <f t="shared" si="9"/>
+      <c r="J6" s="49">
+        <f t="shared" si="2"/>
         <v>0.32500000000000001</v>
       </c>
-      <c r="K6" s="20">
-        <f t="shared" si="10"/>
+      <c r="K6" s="52">
+        <f t="shared" si="3"/>
         <v>0.30353817504655495</v>
       </c>
-      <c r="L6" s="19">
-        <f t="shared" si="11"/>
+      <c r="L6" s="46">
+        <f t="shared" si="4"/>
         <v>251.685</v>
       </c>
-      <c r="M6" s="20">
-        <f t="shared" si="12"/>
+      <c r="M6" s="54">
+        <f t="shared" si="5"/>
         <v>250.08857142857144</v>
       </c>
     </row>
-    <row r="7" ht="14.65">
-      <c r="A7" s="13">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A7" s="7">
         <v>1500</v>
       </c>
-      <c r="B7" s="23">
+      <c r="B7" s="17">
         <f>31.9*10</f>
         <v>319</v>
       </c>
-      <c r="C7" s="24">
-        <f t="shared" si="13"/>
+      <c r="C7" s="18">
+        <f t="shared" si="6"/>
         <v>1181</v>
       </c>
-      <c r="D7" s="25">
+      <c r="D7" s="19">
         <v>155</v>
       </c>
-      <c r="E7" s="23">
-        <f t="shared" si="14"/>
+      <c r="E7" s="43">
+        <f t="shared" si="7"/>
         <v>3.875</v>
       </c>
-      <c r="F7" s="25">
-        <f t="shared" si="7"/>
+      <c r="F7" s="45">
+        <f t="shared" si="0"/>
         <v>3.7021943573667713</v>
       </c>
-      <c r="G7" s="23">
+      <c r="G7" s="17">
         <v>1186</v>
       </c>
-      <c r="H7" s="24">
-        <f t="shared" si="8"/>
+      <c r="H7" s="18">
+        <f t="shared" si="1"/>
         <v>314</v>
       </c>
-      <c r="I7" s="25">
+      <c r="I7" s="19">
         <v>12</v>
       </c>
-      <c r="J7" s="23">
-        <f t="shared" si="9"/>
-        <v>0.29999999999999999</v>
-      </c>
-      <c r="K7" s="25">
-        <f t="shared" si="10"/>
+      <c r="J7" s="50">
+        <f t="shared" si="2"/>
+        <v>0.3</v>
+      </c>
+      <c r="K7" s="53">
+        <f t="shared" si="3"/>
         <v>0.26475548060708265</v>
       </c>
-      <c r="L7" s="23">
-        <f t="shared" si="11"/>
+      <c r="L7" s="47">
+        <f t="shared" si="4"/>
         <v>251.15933333333334</v>
       </c>
-      <c r="M7" s="25">
-        <f t="shared" si="12"/>
+      <c r="M7" s="55">
+        <f t="shared" si="5"/>
         <v>248.26933333333332</v>
       </c>
     </row>
-    <row r="13">
-      <c r="L13" s="5"/>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="L13" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="B1:F1"/>
     <mergeCell ref="G1:K1"/>
   </mergeCells>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="14.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:O8"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col customWidth="1" min="2" max="2" width="9.46484375"/>
-    <col customWidth="1" min="8" max="8" width="9.86328125"/>
-    <col customWidth="1" min="9" max="10" width="11.19921875"/>
-    <col customWidth="1" min="12" max="12" width="18.53125"/>
-    <col customWidth="1" min="13" max="13" width="18.265625"/>
-    <col customWidth="1" min="14" max="14" width="16.3984375"/>
-    <col customWidth="1" min="15" max="15" width="14.53125"/>
+    <col min="2" max="2" width="9.46484375" customWidth="1"/>
+    <col min="8" max="8" width="9.86328125" customWidth="1"/>
+    <col min="9" max="10" width="11.19921875" customWidth="1"/>
+    <col min="12" max="12" width="18.53125" customWidth="1"/>
+    <col min="13" max="13" width="18.265625" customWidth="1"/>
+    <col min="14" max="14" width="16.3984375" customWidth="1"/>
+    <col min="15" max="15" width="14.53125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.65">
-      <c r="B1" s="10" t="s">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="B1" s="35" t="s">
         <v>23</v>
       </c>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="26" t="s">
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="39" t="s">
         <v>24</v>
       </c>
-      <c r="H1" s="27"/>
-      <c r="I1" s="27"/>
-      <c r="J1" s="27"/>
-      <c r="K1" s="28"/>
-    </row>
-    <row r="2" ht="16.899999999999999" customHeight="1">
-      <c r="A2" s="13" t="s">
+      <c r="H1" s="40"/>
+      <c r="I1" s="40"/>
+      <c r="J1" s="40"/>
+      <c r="K1" s="41"/>
+    </row>
+    <row r="2" spans="1:15" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="29" t="s">
+      <c r="B2" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="C2" s="30" t="s">
+      <c r="C2" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="D2" s="31" t="s">
+      <c r="D2" s="22" t="s">
         <v>37</v>
       </c>
-      <c r="E2" s="14" t="s">
+      <c r="E2" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="F2" s="16" t="s">
+      <c r="F2" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="G2" s="29" t="s">
+      <c r="G2" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="H2" s="30" t="s">
+      <c r="H2" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="I2" s="32" t="s">
+      <c r="I2" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="J2" s="14" t="s">
+      <c r="J2" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="K2" s="16" t="s">
+      <c r="K2" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="L2" s="33" t="s">
+      <c r="L2" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="M2" s="16" t="s">
+      <c r="M2" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="N2" s="34" t="s">
+      <c r="N2" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="O2" s="35" t="s">
+      <c r="O2" s="26" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="3" ht="14.65">
-      <c r="A3" s="36">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A3" s="27">
         <v>600</v>
       </c>
-      <c r="B3" s="37">
+      <c r="B3" s="28">
         <v>139</v>
       </c>
-      <c r="C3" s="38">
-        <f t="shared" ref="C3:C6" si="15">A3-B3</f>
+      <c r="C3" s="29">
+        <f t="shared" ref="C3:C6" si="0">A3-B3</f>
         <v>461</v>
       </c>
-      <c r="D3" s="22">
+      <c r="D3" s="16">
         <v>146</v>
       </c>
-      <c r="E3" s="21">
-        <f t="shared" ref="E3:E6" si="16">D3/40</f>
-        <v>3.6499999999999999</v>
-      </c>
-      <c r="F3" s="22">
-        <f t="shared" ref="F3:F6" si="17">C3/B3</f>
+      <c r="E3" s="15">
+        <f t="shared" ref="E3:E6" si="1">D3/40</f>
+        <v>3.65</v>
+      </c>
+      <c r="F3" s="16">
+        <f t="shared" ref="F3:F6" si="2">C3/B3</f>
         <v>3.3165467625899279</v>
       </c>
-      <c r="G3" s="21">
+      <c r="G3" s="15">
         <v>467</v>
       </c>
-      <c r="H3" s="38">
-        <f t="shared" ref="H3:H6" si="18">A3-G3</f>
+      <c r="H3" s="29">
+        <f t="shared" ref="H3:H6" si="3">A3-G3</f>
         <v>133</v>
       </c>
-      <c r="I3" s="22">
+      <c r="I3" s="16">
         <v>13</v>
       </c>
-      <c r="J3" s="21">
-        <f t="shared" ref="J3:J6" si="19">I3/40</f>
+      <c r="J3" s="15">
+        <f t="shared" ref="J3:J6" si="4">I3/40</f>
         <v>0.32500000000000001</v>
       </c>
-      <c r="K3" s="22">
-        <f t="shared" ref="K3:K6" si="20">H3/G3</f>
+      <c r="K3" s="16">
+        <f t="shared" ref="K3:K6" si="5">H3/G3</f>
         <v>0.28479657387580298</v>
       </c>
-      <c r="L3" s="22">
-        <f t="shared" ref="L3:L6" si="21">(B3*C3)/(B3+C3)</f>
+      <c r="L3" s="59">
+        <f t="shared" ref="L3:L6" si="6">(B3*C3)/(B3+C3)</f>
         <v>106.79833333333333</v>
       </c>
-      <c r="M3" s="39">
-        <f t="shared" ref="M3:M6" si="22">(G3*H3)/(G3+H3)</f>
+      <c r="M3" s="60">
+        <f t="shared" ref="M3:M6" si="7">(G3*H3)/(G3+H3)</f>
         <v>103.51833333333333</v>
       </c>
-      <c r="N3" s="40" t="s">
+      <c r="N3" s="30" t="s">
         <v>38</v>
       </c>
-      <c r="O3" s="40" t="s">
+      <c r="O3" s="30" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="41">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A4" s="31">
         <v>550</v>
       </c>
-      <c r="B4" s="42">
+      <c r="B4" s="32">
         <v>146</v>
       </c>
       <c r="C4">
-        <f t="shared" si="15"/>
+        <f t="shared" si="0"/>
         <v>404</v>
       </c>
-      <c r="D4" s="20">
+      <c r="D4" s="14">
         <v>120</v>
       </c>
-      <c r="E4" s="19">
-        <f t="shared" si="16"/>
+      <c r="E4" s="13">
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="F4" s="20">
-        <f t="shared" si="17"/>
+      <c r="F4" s="14">
+        <f t="shared" si="2"/>
         <v>2.7671232876712328</v>
       </c>
-      <c r="G4" s="19">
+      <c r="G4" s="13">
         <v>413</v>
       </c>
       <c r="H4">
-        <f t="shared" si="18"/>
+        <f t="shared" si="3"/>
         <v>137</v>
       </c>
-      <c r="I4" s="20">
+      <c r="I4" s="14">
         <v>15</v>
       </c>
-      <c r="J4" s="19">
-        <f t="shared" si="19"/>
+      <c r="J4" s="13">
+        <f t="shared" si="4"/>
         <v>0.375</v>
       </c>
-      <c r="K4" s="20">
-        <f t="shared" si="20"/>
+      <c r="K4" s="14">
+        <f t="shared" si="5"/>
         <v>0.33171912832929784</v>
       </c>
-      <c r="L4" s="20">
-        <f t="shared" si="21"/>
+      <c r="L4" s="54">
+        <f t="shared" si="6"/>
         <v>107.24363636363637</v>
       </c>
-      <c r="M4" s="43">
-        <f t="shared" si="22"/>
+      <c r="M4" s="61">
+        <f t="shared" si="7"/>
         <v>102.87454545454545</v>
       </c>
-      <c r="N4" s="44"/>
-      <c r="O4" s="44"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="41">
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A5" s="31">
         <v>500</v>
       </c>
-      <c r="B5" s="42">
+      <c r="B5" s="32">
         <v>155</v>
       </c>
       <c r="C5">
-        <f t="shared" si="15"/>
+        <f t="shared" si="0"/>
         <v>345</v>
       </c>
-      <c r="D5" s="20">
+      <c r="D5" s="14">
         <v>98</v>
       </c>
-      <c r="E5" s="19">
-        <f t="shared" si="16"/>
+      <c r="E5" s="13">
+        <f t="shared" si="1"/>
         <v>2.4500000000000002</v>
       </c>
-      <c r="F5" s="20">
-        <f t="shared" si="17"/>
+      <c r="F5" s="14">
+        <f t="shared" si="2"/>
         <v>2.225806451612903</v>
       </c>
-      <c r="G5" s="19">
+      <c r="G5" s="13">
         <v>355</v>
       </c>
       <c r="H5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="3"/>
         <v>145</v>
       </c>
-      <c r="I5" s="20">
+      <c r="I5" s="14">
         <v>19</v>
       </c>
-      <c r="J5" s="19">
-        <f t="shared" si="19"/>
+      <c r="J5" s="13">
+        <f t="shared" si="4"/>
         <v>0.47499999999999998</v>
       </c>
-      <c r="K5" s="20">
-        <f t="shared" si="20"/>
+      <c r="K5" s="14">
+        <f t="shared" si="5"/>
         <v>0.40845070422535212</v>
       </c>
-      <c r="L5" s="20">
-        <f t="shared" si="21"/>
+      <c r="L5" s="54">
+        <f t="shared" si="6"/>
         <v>106.95</v>
       </c>
-      <c r="M5" s="43">
-        <f t="shared" si="22"/>
+      <c r="M5" s="61">
+        <f t="shared" si="7"/>
         <v>102.95</v>
       </c>
-      <c r="N5" s="44"/>
-      <c r="O5" s="44"/>
-    </row>
-    <row r="6" ht="14.65">
-      <c r="A6" s="45">
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A6" s="33">
         <v>450</v>
       </c>
-      <c r="B6" s="46">
+      <c r="B6" s="34">
         <v>173</v>
       </c>
-      <c r="C6" s="24">
-        <f t="shared" si="15"/>
+      <c r="C6" s="18">
+        <f t="shared" si="0"/>
         <v>277</v>
       </c>
-      <c r="D6" s="25">
+      <c r="D6" s="19">
         <v>68</v>
       </c>
-      <c r="E6" s="23">
-        <f t="shared" si="16"/>
+      <c r="E6" s="17">
+        <f t="shared" si="1"/>
         <v>1.7</v>
       </c>
-      <c r="F6" s="25">
-        <f t="shared" si="17"/>
+      <c r="F6" s="19">
+        <f t="shared" si="2"/>
         <v>1.6011560693641618</v>
       </c>
-      <c r="G6" s="23">
+      <c r="G6" s="17">
         <v>285</v>
       </c>
-      <c r="H6" s="24">
-        <f t="shared" si="18"/>
+      <c r="H6" s="18">
+        <f t="shared" si="3"/>
         <v>165</v>
       </c>
-      <c r="I6" s="25">
+      <c r="I6" s="19">
         <v>26</v>
       </c>
-      <c r="J6" s="23">
-        <f t="shared" si="19"/>
-        <v>0.65000000000000002</v>
-      </c>
-      <c r="K6" s="25">
-        <f t="shared" si="20"/>
+      <c r="J6" s="17">
+        <f t="shared" si="4"/>
+        <v>0.65</v>
+      </c>
+      <c r="K6" s="19">
+        <f t="shared" si="5"/>
         <v>0.57894736842105265</v>
       </c>
-      <c r="L6" s="25">
-        <f t="shared" si="21"/>
+      <c r="L6" s="55">
+        <f t="shared" si="6"/>
         <v>106.49111111111111</v>
       </c>
-      <c r="M6" s="47">
-        <f t="shared" si="22"/>
+      <c r="M6" s="62">
+        <f t="shared" si="7"/>
         <v>104.5</v>
       </c>
-      <c r="N6" s="44"/>
-      <c r="O6" s="44"/>
-    </row>
-    <row r="7">
-      <c r="C7" s="44"/>
-      <c r="D7" s="44"/>
-    </row>
-    <row r="8">
-      <c r="D8" s="5"/>
-    </row>
-    <row r="9">
-      <c r="C9" s="44"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="D8" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="B1:F1"/>
     <mergeCell ref="G1:K1"/>
   </mergeCells>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
--- a/Banco ottico.xlsx
+++ b/Banco ottico.xlsx
@@ -1,77 +1,60 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimibit-my.sharepoint.com/personal/m_declich_campus_unimib_it/Documents/Documenti/Università/I° anno/Laboratorio I/Esperienze in laboratorio/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="99" documentId="11_2BDBA90D71226A740C9D53B8AF822B342D3B3C81" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CD78A13D-9B4E-49A4-8FBD-4142FDDA0BBD}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="2"/>
   </bookViews>
   <sheets>
-    <sheet name="Angoli di rifrazione" sheetId="1" r:id="rId1"/>
-    <sheet name="Distanze" sheetId="2" r:id="rId2"/>
-    <sheet name="Distanze focali (250mm)" sheetId="3" r:id="rId3"/>
-    <sheet name="Distanze focali (100mm)" sheetId="4" r:id="rId4"/>
+    <sheet name="Angoli di rifrazione" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Distanze" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Distanze focali (250mm)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Distanze focali (100mm)" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{D0CA8CA8-9F24-4464-BF8E-62219DCF47F9}"/>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="40">
-  <si>
-    <t>Lato piatto</t>
-  </si>
-  <si>
-    <t>Lato curvo</t>
-  </si>
-  <si>
-    <t>θ inc</t>
-  </si>
-  <si>
-    <t>sinθ inc</t>
-  </si>
-  <si>
-    <t>θ rif</t>
-  </si>
-  <si>
-    <t>sinθ rif</t>
-  </si>
-  <si>
-    <t>θ critico</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
+  <si>
+    <t xml:space="preserve">Lato piatto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lato curvo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">θ inc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sinθ inc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">θ rif</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sinθ rif</t>
+  </si>
+  <si>
+    <t xml:space="preserve">θ critico</t>
   </si>
   <si>
     <t>Reversibilità</t>
   </si>
   <si>
-    <t>θ' inc</t>
-  </si>
-  <si>
-    <t>θ' rif</t>
-  </si>
-  <si>
-    <t>δ minimo (rad)</t>
-  </si>
-  <si>
-    <t>α (rad)</t>
+    <t xml:space="preserve">θ' inc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">θ' rif</t>
+  </si>
+  <si>
+    <t xml:space="preserve">δ minimo (rad)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">α (rad)</t>
   </si>
   <si>
     <t>n</t>
@@ -80,25 +63,25 @@
     <t>σn</t>
   </si>
   <si>
-    <t>prisma a base triangolare</t>
-  </si>
-  <si>
-    <t>prisma a base trapezioidale</t>
-  </si>
-  <si>
-    <t>h prisma trapezoidale</t>
-  </si>
-  <si>
-    <t>32mm (1mm)</t>
+    <t xml:space="preserve">prisma a base triangolare</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prisma a base trapezioidale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">h prisma trapezoidale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32mm (1mm)</t>
   </si>
   <si>
     <t>ANGOLI</t>
   </si>
   <si>
-    <t>Distanza dal centro [mm]</t>
-  </si>
-  <si>
-    <t>Distanza attesa [mm]</t>
+    <t xml:space="preserve">Distanza dal centro [mm]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Distanza attesa [mm]</t>
   </si>
   <si>
     <t>Seno</t>
@@ -107,82 +90,82 @@
     <t>Coseno</t>
   </si>
   <si>
-    <t>Fuoco 1</t>
-  </si>
-  <si>
-    <t>Fuoco 2</t>
-  </si>
-  <si>
-    <t>D totale</t>
-  </si>
-  <si>
-    <t>p (mm)</t>
-  </si>
-  <si>
-    <t>q (mm)</t>
-  </si>
-  <si>
-    <t>h' (mm)</t>
-  </si>
-  <si>
-    <t>M misurato</t>
-  </si>
-  <si>
-    <t>M atteso</t>
-  </si>
-  <si>
-    <t>DISTANZA FOCALE 1</t>
-  </si>
-  <si>
-    <t>DISTANZA FOCALE 2</t>
-  </si>
-  <si>
-    <t>D. MINIMA OSS.</t>
-  </si>
-  <si>
-    <t>D. MINIMA TEOR.</t>
+    <t xml:space="preserve">Fuoco 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fuoco 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D totale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p (mm)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">q (mm)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">h' (mm)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M misurato</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M atteso</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DISTANZA FOCALE 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DISTANZA FOCALE 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D. MINIMA OSS.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D. MINIMA TEOR.</t>
   </si>
   <si>
     <t>999mm</t>
   </si>
   <si>
-    <t>1000 mm</t>
+    <t xml:space="preserve">1000 mm</t>
   </si>
   <si>
     <t>h'</t>
   </si>
   <si>
-    <t>405 mm</t>
-  </si>
-  <si>
-    <t>400 mm</t>
+    <t xml:space="preserve">405 mm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">400 mm</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="164" formatCode="0.000"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
-    <numFmt numFmtId="166" formatCode="0.000"/>
+    <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
-      <sz val="11"/>
+      <sz val="11.000000"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
     <font>
       <u/>
-      <sz val="11"/>
+      <sz val="11.000000"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -197,176 +180,316 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.499984740745262"/>
-        <bgColor theme="3" tint="0.499984740745262"/>
+        <fgColor rgb="FF4285F4"/>
+        <bgColor rgb="FF4285F4"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor indexed="5"/>
+        <fgColor rgb="FFC00000"/>
+        <bgColor rgb="FFC00000"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor indexed="2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF00B050"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor rgb="FFFFC000"/>
+        <bgColor rgb="FFFFC000"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="16">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
+  <borders count="33">
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
     </border>
     <border>
       <left style="medium">
-        <color auto="1"/>
+        <color theme="1"/>
       </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right/>
+      <right style="none"/>
       <top style="medium">
-        <color auto="1"/>
+        <color theme="1"/>
       </top>
       <bottom style="medium">
-        <color auto="1"/>
+        <color theme="1"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
       <top style="medium">
-        <color auto="1"/>
+        <color theme="1"/>
       </top>
       <bottom style="medium">
-        <color auto="1"/>
+        <color theme="1"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
       <right style="medium">
-        <color auto="1"/>
+        <color theme="1"/>
       </right>
       <top style="medium">
-        <color auto="1"/>
+        <color theme="1"/>
       </top>
       <bottom style="medium">
-        <color auto="1"/>
+        <color theme="1"/>
       </bottom>
-      <diagonal/>
+      <diagonal style="none"/>
     </border>
     <border>
       <left style="medium">
-        <color auto="1"/>
+        <color theme="1"/>
       </left>
-      <right/>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
       <right style="medium">
-        <color auto="1"/>
+        <color theme="1"/>
       </right>
       <top style="medium">
-        <color auto="1"/>
+        <color theme="1"/>
       </top>
-      <bottom/>
-      <diagonal/>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
     </border>
     <border>
       <left style="medium">
-        <color auto="1"/>
+        <color theme="1"/>
       </left>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
+      <right style="none"/>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
       <right style="medium">
-        <color auto="1"/>
+        <color theme="1"/>
       </right>
-      <top/>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top style="medium">
-        <color auto="1"/>
+        <color theme="1"/>
       </top>
-      <bottom/>
-      <diagonal/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
     </border>
     <border>
       <left style="medium">
-        <color auto="1"/>
+        <color theme="1"/>
       </left>
       <right style="medium">
-        <color auto="1"/>
+        <color theme="1"/>
+      </right>
+      <top style="none"/>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="1"/>
+      </left>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="1"/>
+      </left>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="none"/>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="1"/>
+      </left>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="1"/>
+      </left>
+      <right style="medium">
+        <color theme="1"/>
       </right>
       <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="medium">
         <color auto="1"/>
       </top>
       <bottom style="medium">
         <color auto="1"/>
       </bottom>
-      <diagonal/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="none"/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="none"/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="none"/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
     </border>
     <border>
       <left style="medium">
@@ -378,8 +501,36 @@
       <top style="medium">
         <color auto="1"/>
       </top>
-      <bottom/>
-      <diagonal/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="1"/>
+      </left>
+      <right style="none"/>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium">
+        <color theme="1"/>
+      </right>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal style="none"/>
     </border>
     <border>
       <left style="medium">
@@ -388,9 +539,9 @@
       <right style="medium">
         <color auto="1"/>
       </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
     </border>
     <border>
       <left style="medium">
@@ -399,102 +550,174 @@
       <right style="medium">
         <color auto="1"/>
       </right>
-      <top/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="none"/>
       <bottom style="medium">
         <color auto="1"/>
       </bottom>
-      <diagonal/>
+      <diagonal style="none"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="63">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+  <cellXfs count="104">
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
+    <xf fontId="0" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="2" borderId="2" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="2" borderId="3" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="3" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="2" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="4" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="5" numFmtId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="6" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="6" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="7" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="8" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="9" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1"/>
+    <xf fontId="0" fillId="0" borderId="10" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="11" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="12" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="12" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="13" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="3" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf fontId="0" fillId="0" borderId="5" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="7" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="10" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="13" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="4" borderId="2" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="4" borderId="3" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="5" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="5" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="7" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="6" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="7" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1" quotePrefix="1"/>
+    <xf fontId="0" fillId="3" borderId="11" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="11" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="13" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="12" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="13" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1" quotePrefix="1"/>
+    <xf fontId="0" fillId="5" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="5" borderId="3" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="6" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="7" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="5" borderId="14" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1"/>
+    <xf fontId="0" fillId="5" borderId="8" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="4" borderId="15" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="4" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="4" borderId="16" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="5" borderId="17" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="18" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="18" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="19" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="20" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="17" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf fontId="0" fillId="3" borderId="6" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="3" borderId="7" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="14" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="16" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="15" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="16" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="15" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="21" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="22" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="15" numFmtId="166" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="166" xfId="0" applyNumberFormat="1"/>
+    <xf fontId="0" fillId="0" borderId="8" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="12" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="13" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="15" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="16" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="16" numFmtId="166" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="23" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="24" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="25" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="24" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="25" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="25" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="24" numFmtId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="25" numFmtId="166" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="24" numFmtId="166" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="4" borderId="20" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="4" borderId="18" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="4" borderId="19" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="5" borderId="4" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="26" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="22" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="21" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="16" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="27" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="3" borderId="20" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf fontId="0" fillId="3" borderId="28" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf fontId="0" fillId="3" borderId="29" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf fontId="0" fillId="0" borderId="30" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="26" numFmtId="166" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="26" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="22" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="21" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="22" numFmtId="166" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="31" numFmtId="166" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="18" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf fontId="0" fillId="0" borderId="11" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="30" numFmtId="166" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="32" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="23" numFmtId="166" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="32" numFmtId="166" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -512,8 +735,291 @@
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="1F497D"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="EEECE1"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4F81BD"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="C0504D"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="9BBB59"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8064A2"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4BACC6"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="F79646"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000FF"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="800080"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Cambria"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Angsana New"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ 明朝"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Cordia New"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="1"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+</a:theme>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema di Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" name="Tema di Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -724,233 +1230,231 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I16"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="4.46484375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.1328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.796875" bestFit="1"/>
-    <col min="4" max="4" width="11.1328125" bestFit="1"/>
-    <col min="5" max="5" width="4.796875" bestFit="1"/>
-    <col min="6" max="6" width="11.1328125" bestFit="1"/>
-    <col min="7" max="7" width="6.86328125" bestFit="1"/>
+    <col bestFit="1" customWidth="1" min="1" max="1" width="4.46484375"/>
+    <col customWidth="1" min="2" max="2" width="8.125"/>
+    <col bestFit="1" min="3" max="3" width="4.796875"/>
+    <col bestFit="1" min="4" max="4" width="11.1328125"/>
+    <col bestFit="1" min="5" max="5" width="4.796875"/>
+    <col bestFit="1" min="6" max="6" width="11.1328125"/>
+    <col bestFit="1" min="7" max="7" width="6.86328125"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="C1" s="38" t="s">
+    <row r="1">
+      <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38" t="s">
+      <c r="D1" s="2"/>
+      <c r="E1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="38"/>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A2" s="1" t="s">
+      <c r="F1" s="3"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="6" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A3" s="2">
+    <row r="3">
+      <c r="A3" s="7">
         <v>20</v>
       </c>
-      <c r="B3" s="57">
+      <c r="B3" s="8">
         <f t="shared" ref="B3:B8" si="0">SIN((A3*PI())/180)</f>
         <v>0.34202014332566871</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="9">
         <v>13</v>
       </c>
-      <c r="D3" s="57">
+      <c r="D3" s="8">
         <f t="shared" ref="D3:D8" si="1">SIN((C3*PI())/180)</f>
         <v>0.224951054343865</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="9">
         <v>30</v>
       </c>
-      <c r="F3" s="57">
+      <c r="F3" s="10">
         <f t="shared" ref="F3:F8" si="2">SIN((E3*PI())/180)</f>
         <v>0.49999999999999994</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="11">
         <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A4">
+    <row r="4">
+      <c r="A4" s="12">
         <v>25</v>
       </c>
-      <c r="B4" s="57">
+      <c r="B4" s="13">
         <f t="shared" si="0"/>
         <v>0.42261826174069944</v>
       </c>
       <c r="C4">
         <v>16</v>
       </c>
-      <c r="D4" s="57">
+      <c r="D4" s="13">
         <f t="shared" si="1"/>
         <v>0.27563735581699916</v>
       </c>
       <c r="E4">
         <v>39</v>
       </c>
-      <c r="F4" s="57">
+      <c r="F4" s="14">
         <f t="shared" si="2"/>
         <v>0.62932039104983739</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A5">
+    <row r="5">
+      <c r="A5" s="12">
         <v>30</v>
       </c>
-      <c r="B5" s="57">
+      <c r="B5" s="13">
         <f t="shared" si="0"/>
         <v>0.49999999999999994</v>
       </c>
       <c r="C5">
         <v>20</v>
       </c>
-      <c r="D5" s="57">
+      <c r="D5" s="13">
         <f t="shared" si="1"/>
         <v>0.34202014332566871</v>
       </c>
       <c r="E5">
         <v>48</v>
       </c>
-      <c r="F5" s="57">
+      <c r="F5" s="14">
         <f t="shared" si="2"/>
         <v>0.74314482547739413</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A6">
+    <row r="6">
+      <c r="A6" s="12">
         <v>45</v>
       </c>
-      <c r="B6" s="57">
+      <c r="B6" s="13">
         <f t="shared" si="0"/>
         <v>0.70710678118654746</v>
       </c>
       <c r="C6">
         <v>28</v>
       </c>
-      <c r="D6" s="57">
+      <c r="D6" s="13">
         <f t="shared" si="1"/>
         <v>0.46947156278589081</v>
       </c>
       <c r="E6">
         <v>136</v>
       </c>
-      <c r="F6" s="57">
+      <c r="F6" s="14">
         <f t="shared" si="2"/>
         <v>0.69465837045899714</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A7">
+    <row r="7">
+      <c r="A7" s="12">
         <v>60</v>
       </c>
-      <c r="B7" s="57">
+      <c r="B7" s="13">
         <f t="shared" si="0"/>
         <v>0.8660254037844386</v>
       </c>
       <c r="C7">
         <v>35</v>
       </c>
-      <c r="D7" s="57">
+      <c r="D7" s="13">
         <f t="shared" si="1"/>
         <v>0.57357643635104605</v>
       </c>
       <c r="E7">
         <v>120</v>
       </c>
-      <c r="F7" s="57">
+      <c r="F7" s="14">
         <f t="shared" si="2"/>
         <v>0.86602540378443871</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A8">
+    <row r="8">
+      <c r="A8" s="15">
         <v>70</v>
       </c>
-      <c r="B8" s="57">
+      <c r="B8" s="16">
         <f t="shared" si="0"/>
         <v>0.93969262078590832</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="17">
         <v>39</v>
       </c>
-      <c r="D8" s="57">
+      <c r="D8" s="16">
         <f t="shared" si="1"/>
         <v>0.62932039104983739</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="17">
         <v>111</v>
       </c>
-      <c r="F8" s="57">
+      <c r="F8" s="18">
         <f t="shared" si="2"/>
         <v>0.93358042649720174</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A10" s="38" t="s">
+    <row r="10">
+      <c r="A10" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="38"/>
-      <c r="C10" s="1" t="s">
+      <c r="B10" s="3"/>
+      <c r="C10" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D10" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="E10" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="F10" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="I10" s="3"/>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="C11">
+      <c r="I10" s="20"/>
+    </row>
+    <row r="11">
+      <c r="C11" s="21">
         <v>13</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="9">
         <v>19</v>
       </c>
-      <c r="E11">
+      <c r="E11" s="9">
         <v>30</v>
       </c>
-      <c r="F11">
+      <c r="F11" s="22">
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="C12">
+    <row r="12">
+      <c r="C12" s="12">
         <v>16</v>
       </c>
       <c r="D12">
@@ -959,12 +1463,12 @@
       <c r="E12">
         <v>25</v>
       </c>
-      <c r="F12">
+      <c r="F12" s="23">
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="C13">
+    <row r="13">
+      <c r="C13" s="12">
         <v>20</v>
       </c>
       <c r="D13">
@@ -973,12 +1477,12 @@
       <c r="E13">
         <v>48</v>
       </c>
-      <c r="F13">
+      <c r="F13" s="23">
         <v>30</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="C14">
+    <row r="14">
+      <c r="C14" s="12">
         <v>28</v>
       </c>
       <c r="D14">
@@ -987,12 +1491,12 @@
       <c r="E14">
         <v>136</v>
       </c>
-      <c r="F14">
+      <c r="F14" s="23">
         <v>45</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="C15">
+    <row r="15">
+      <c r="C15" s="12">
         <v>35</v>
       </c>
       <c r="D15">
@@ -1001,21 +1505,21 @@
       <c r="E15">
         <v>121</v>
       </c>
-      <c r="F15">
+      <c r="F15" s="23">
         <v>58</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="C16">
+    <row r="16">
+      <c r="C16" s="15">
         <v>39</v>
       </c>
-      <c r="D16">
+      <c r="D16" s="17">
         <v>68</v>
       </c>
-      <c r="E16">
+      <c r="E16" s="17">
         <v>111</v>
       </c>
-      <c r="F16">
+      <c r="F16" s="24">
         <v>69</v>
       </c>
     </row>
@@ -1025,844 +1529,856 @@
     <mergeCell ref="E1:F1"/>
     <mergeCell ref="A10:B10"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E12"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="23.46484375" customWidth="1"/>
-    <col min="2" max="2" width="20.59765625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.59765625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.3984375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.265625" bestFit="1" customWidth="1"/>
+    <col customWidth="1" min="1" max="1" width="23.46484375"/>
+    <col bestFit="1" customWidth="1" min="2" max="2" width="20.59765625"/>
+    <col bestFit="1" customWidth="1" min="3" max="3" width="17.59765625"/>
+    <col bestFit="1" customWidth="1" min="4" max="4" width="12.3984375"/>
+    <col bestFit="1" customWidth="1" min="5" max="5" width="10.265625"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="1">
       <c r="B1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="26" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A2" s="4" t="s">
+    <row r="2">
+      <c r="A2" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="58">
+      <c r="B2" s="28">
         <f>PI()/4</f>
         <v>0.78539816339744828</v>
       </c>
-      <c r="C2" s="58">
+      <c r="C2" s="29">
         <f>PI()/3</f>
         <v>1.0471975511965976</v>
       </c>
-      <c r="D2" s="58">
-        <f t="shared" ref="D2:D3" si="0">(SIN((B2/2)+(C2/2))/(SIN(C2/2)))</f>
+      <c r="D2" s="30">
+        <f t="shared" ref="D2:D3" si="3">(SIN((B2/2)+(C2/2))/(SIN(C2/2)))</f>
         <v>1.5867066805824706</v>
       </c>
-      <c r="E2" s="56">
-        <f t="shared" ref="E2:E3" si="1">((1/(2*SIN(C2/2)))*COS(((PI()/180)+C2)/2))*((PI()/180))</f>
-        <v>1.5038265780899104E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A3" s="4" t="s">
+      <c r="E2" s="31">
+        <f>((1/(2*SIN(C2/2)))*COS(((PI()/180)+C2)/2))*((PI()/180))</f>
+        <v>1.5038265780899108e-002</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="58">
+      <c r="B3" s="33">
         <f>(27*PI())/180</f>
         <v>0.47123889803846897</v>
       </c>
-      <c r="C3" s="58">
+      <c r="C3" s="34">
         <f>PI()/4</f>
         <v>0.78539816339744828</v>
       </c>
-      <c r="D3" s="58">
-        <f t="shared" si="0"/>
+      <c r="D3" s="35">
+        <f t="shared" si="3"/>
         <v>1.5359568838917252</v>
       </c>
-      <c r="E3" s="56">
-        <f t="shared" si="1"/>
-        <v>2.0991032162068827E-2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A5" s="6" t="s">
+      <c r="E3" s="36">
+        <f>((1/(2*SIN(C3/2)))*COS(((PI()/180)+C3)/2))*((PI()/180))</f>
+        <v>2.0991032162068827e-002</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="37" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="38" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A7" s="4" t="s">
+    <row r="7">
+      <c r="A7" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="40" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A8" s="4">
+    <row r="8">
+      <c r="A8" s="41">
         <v>10</v>
       </c>
       <c r="B8">
         <v>2</v>
       </c>
-      <c r="C8" s="58">
+      <c r="C8" s="42">
         <f>32*D8*(1-(E8/SQRT(D3^2-D8^2)))</f>
         <v>1.9709421734493859</v>
       </c>
-      <c r="D8" s="57">
-        <f t="shared" ref="D8:D12" si="2">SIN((A8*PI())/180)</f>
+      <c r="D8" s="13">
+        <f t="shared" ref="D8:D12" si="4">SIN((A8*PI())/180)</f>
         <v>0.17364817766693033</v>
       </c>
-      <c r="E8" s="57">
-        <f t="shared" ref="E8:E12" si="3">COS((A8*PI())/180)</f>
+      <c r="E8" s="14">
+        <f t="shared" ref="E8:E12" si="5">COS((A8*PI())/180)</f>
         <v>0.98480775301220802</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A9" s="4">
+    <row r="9">
+      <c r="A9" s="41">
         <v>20</v>
       </c>
       <c r="B9">
         <v>4</v>
       </c>
-      <c r="C9" s="58">
+      <c r="C9" s="42">
         <f>32*D9*(1-(E9/SQRT(D3^2-D9^2)))</f>
         <v>4.0763062050074748</v>
       </c>
-      <c r="D9" s="57">
-        <f t="shared" si="2"/>
+      <c r="D9" s="13">
+        <f>SIN((A9*PI())/180)</f>
         <v>0.34202014332566871</v>
       </c>
-      <c r="E9" s="57">
-        <f t="shared" si="3"/>
+      <c r="E9" s="14">
+        <f t="shared" si="5"/>
         <v>0.93969262078590843</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A10" s="4">
+    <row r="10">
+      <c r="A10" s="41">
         <v>30</v>
       </c>
       <c r="B10">
         <v>6</v>
       </c>
-      <c r="C10" s="58">
+      <c r="C10" s="42">
         <f>32*D10*(1-(E10/SQRT(D3^2-D10^2)))</f>
         <v>6.4589650713431856</v>
       </c>
-      <c r="D10" s="57">
-        <f t="shared" si="2"/>
+      <c r="D10" s="13">
+        <f t="shared" si="4"/>
         <v>0.49999999999999994</v>
       </c>
-      <c r="E10" s="57">
-        <f t="shared" si="3"/>
+      <c r="E10" s="14">
+        <f t="shared" si="5"/>
         <v>0.86602540378443871</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A11" s="4">
+    <row r="11">
+      <c r="A11" s="41">
         <v>40</v>
       </c>
       <c r="B11">
         <v>9</v>
       </c>
-      <c r="C11" s="58">
+      <c r="C11" s="42">
         <f>32*D11*(1-(E11/SQRT(D3^2-D11^2)))</f>
         <v>9.2738090225061391</v>
       </c>
-      <c r="D11" s="57">
-        <f t="shared" si="2"/>
+      <c r="D11" s="13">
+        <f t="shared" si="4"/>
         <v>0.64278760968653925</v>
       </c>
-      <c r="E11" s="57">
-        <f t="shared" si="3"/>
+      <c r="E11" s="14">
+        <f t="shared" si="5"/>
         <v>0.76604444311897801</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A12" s="4">
+    <row r="12">
+      <c r="A12" s="43">
         <v>50</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="17">
         <v>12</v>
       </c>
-      <c r="C12" s="58">
+      <c r="C12" s="35">
         <f>32*D12*(1-(E12/SQRT(D3^2-D12^2)))</f>
         <v>12.677612089302682</v>
       </c>
-      <c r="D12" s="57">
-        <f t="shared" si="2"/>
+      <c r="D12" s="16">
+        <f t="shared" si="4"/>
         <v>0.76604444311897801</v>
       </c>
-      <c r="E12" s="57">
-        <f t="shared" si="3"/>
+      <c r="E12" s="18">
+        <f t="shared" si="5"/>
         <v>0.64278760968653936</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:O13"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="8" max="8" width="10.19921875" customWidth="1"/>
-    <col min="9" max="9" width="10.9296875" customWidth="1"/>
-    <col min="10" max="10" width="13.9296875" customWidth="1"/>
-    <col min="11" max="11" width="14.9296875" customWidth="1"/>
-    <col min="12" max="12" width="16.9296875" customWidth="1"/>
-    <col min="13" max="13" width="16.86328125" customWidth="1"/>
-    <col min="14" max="14" width="17" customWidth="1"/>
-    <col min="15" max="15" width="15" customWidth="1"/>
+    <col customWidth="1" min="8" max="8" width="10.19921875"/>
+    <col customWidth="1" min="9" max="9" width="10.9296875"/>
+    <col customWidth="1" min="10" max="10" width="13.9296875"/>
+    <col customWidth="1" min="11" max="11" width="14.9296875"/>
+    <col customWidth="1" min="12" max="12" width="16.9296875"/>
+    <col customWidth="1" min="13" max="13" width="16.86328125"/>
+    <col customWidth="1" min="14" max="14" width="17"/>
+    <col bestFit="1" customWidth="1" min="15" max="15" width="9.00390625"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="B1" s="35" t="s">
+    <row r="1">
+      <c r="B1" s="44" t="s">
         <v>23</v>
       </c>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="37"/>
-      <c r="G1" s="35" t="s">
+      <c r="C1" s="45"/>
+      <c r="D1" s="45"/>
+      <c r="E1" s="45"/>
+      <c r="F1" s="46"/>
+      <c r="G1" s="44" t="s">
         <v>24</v>
       </c>
-      <c r="H1" s="36"/>
-      <c r="I1" s="36"/>
-      <c r="J1" s="36"/>
-      <c r="K1" s="36"/>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A2" s="7" t="s">
+      <c r="H1" s="45"/>
+      <c r="I1" s="45"/>
+      <c r="J1" s="45"/>
+      <c r="K1" s="45"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="47" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="49" t="s">
         <v>27</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D2" s="50" t="s">
         <v>28</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="E2" s="49" t="s">
         <v>29</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="F2" s="49" t="s">
         <v>30</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="G2" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="H2" s="9" t="s">
+      <c r="H2" s="49" t="s">
         <v>27</v>
       </c>
-      <c r="I2" s="10" t="s">
+      <c r="I2" s="50" t="s">
         <v>28</v>
       </c>
-      <c r="J2" s="9" t="s">
+      <c r="J2" s="49" t="s">
         <v>29</v>
       </c>
-      <c r="K2" s="9" t="s">
+      <c r="K2" s="49" t="s">
         <v>30</v>
       </c>
-      <c r="L2" s="8" t="s">
+      <c r="L2" s="51" t="s">
         <v>31</v>
       </c>
-      <c r="M2" s="10" t="s">
+      <c r="M2" s="49" t="s">
         <v>32</v>
       </c>
-      <c r="N2" s="11" t="s">
+      <c r="N2" s="52" t="s">
         <v>33</v>
       </c>
-      <c r="O2" s="12" t="s">
+      <c r="O2" s="53" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A3" s="7">
+      <c r="P2" s="54"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="55">
         <v>1100</v>
       </c>
-      <c r="B3" s="13">
+      <c r="B3">
         <f>39*10</f>
         <v>390</v>
       </c>
       <c r="C3">
         <v>710</v>
       </c>
-      <c r="D3" s="14">
+      <c r="D3" s="56">
         <v>77</v>
       </c>
-      <c r="E3" s="42">
-        <f>D3/40</f>
+      <c r="E3" s="57">
+        <f t="shared" ref="E3:E7" si="6">D3/40</f>
         <v>1.925</v>
       </c>
-      <c r="F3" s="44">
-        <f t="shared" ref="F3:F7" si="0">C3/B3</f>
+      <c r="F3" s="58">
+        <f t="shared" ref="F3:F7" si="7">C3/B3</f>
         <v>1.8205128205128205</v>
       </c>
-      <c r="G3" s="13">
+      <c r="G3" s="59">
         <v>720</v>
       </c>
       <c r="H3">
-        <f t="shared" ref="H3:H7" si="1">A3-G3</f>
+        <f t="shared" ref="H3:H7" si="8">A3-G3</f>
         <v>380</v>
       </c>
-      <c r="I3" s="14">
+      <c r="I3" s="56">
         <v>22</v>
       </c>
-      <c r="J3" s="48">
-        <f t="shared" ref="J3:J7" si="2">I3/40</f>
+      <c r="J3" s="60">
+        <f t="shared" ref="J3:J7" si="9">I3/40</f>
         <v>0.55000000000000004</v>
       </c>
-      <c r="K3" s="51">
-        <f t="shared" ref="K3:K7" si="3">H3/G3</f>
+      <c r="K3" s="61">
+        <f t="shared" ref="K3:K7" si="10">H3/G3</f>
         <v>0.52777777777777779</v>
       </c>
-      <c r="L3" s="46">
-        <f t="shared" ref="L3:L7" si="4">(B3*C3)/(B3+C3)</f>
+      <c r="L3" s="62">
+        <f t="shared" ref="L3:L7" si="11">(B3*C3)/(B3+C3)</f>
         <v>251.72727272727272</v>
       </c>
-      <c r="M3" s="54">
-        <f t="shared" ref="M3:M7" si="5">(G3*H3)/(G3+H3)</f>
+      <c r="M3" s="63">
+        <f t="shared" ref="M3:M7" si="12">(G3*H3)/(G3+H3)</f>
         <v>248.72727272727272</v>
       </c>
-      <c r="N3" t="s">
+      <c r="N3" s="64" t="s">
         <v>35</v>
       </c>
-      <c r="O3" t="s">
+      <c r="O3" s="65" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A4" s="7">
+      <c r="P3" s="66"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="55">
         <v>1200</v>
       </c>
-      <c r="B4" s="13">
+      <c r="B4">
         <f>35.5*10</f>
         <v>355</v>
       </c>
       <c r="C4">
-        <f t="shared" ref="C4:C7" si="6">A4-B4</f>
+        <f t="shared" ref="C4:C7" si="13">A4-B4</f>
         <v>845</v>
       </c>
-      <c r="D4" s="14">
+      <c r="D4" s="56">
         <v>100</v>
       </c>
-      <c r="E4" s="42">
-        <f t="shared" ref="E4:E7" si="7">D4/40</f>
+      <c r="E4" s="57">
+        <f t="shared" si="6"/>
         <v>2.5</v>
       </c>
-      <c r="F4" s="44">
-        <f t="shared" si="0"/>
+      <c r="F4" s="58">
+        <f t="shared" si="7"/>
         <v>2.380281690140845</v>
       </c>
-      <c r="G4" s="13">
+      <c r="G4" s="59">
         <v>850</v>
       </c>
       <c r="H4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="8"/>
         <v>350</v>
       </c>
-      <c r="I4" s="14">
+      <c r="I4" s="56">
         <v>18</v>
       </c>
-      <c r="J4" s="49">
-        <f t="shared" si="2"/>
-        <v>0.45</v>
-      </c>
-      <c r="K4" s="52">
-        <f t="shared" si="3"/>
+      <c r="J4" s="67">
+        <f t="shared" si="9"/>
+        <v>0.45000000000000001</v>
+      </c>
+      <c r="K4" s="68">
+        <f t="shared" si="10"/>
         <v>0.41176470588235292</v>
       </c>
-      <c r="L4" s="46">
-        <f t="shared" si="4"/>
+      <c r="L4" s="62">
+        <f t="shared" si="11"/>
         <v>249.97916666666666</v>
       </c>
-      <c r="M4" s="54">
-        <f t="shared" si="5"/>
+      <c r="M4" s="69">
+        <f t="shared" si="12"/>
         <v>247.91666666666666</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A5" s="7">
+    <row r="5">
+      <c r="A5" s="55">
         <v>1300</v>
       </c>
-      <c r="B5" s="13">
+      <c r="B5">
         <f>34*10</f>
         <v>340</v>
       </c>
       <c r="C5">
+        <f t="shared" si="13"/>
+        <v>960</v>
+      </c>
+      <c r="D5" s="56">
+        <v>119</v>
+      </c>
+      <c r="E5" s="57">
         <f t="shared" si="6"/>
-        <v>960</v>
-      </c>
-      <c r="D5" s="14">
-        <v>119</v>
-      </c>
-      <c r="E5" s="42">
+        <v>2.9750000000000001</v>
+      </c>
+      <c r="F5" s="58">
         <f t="shared" si="7"/>
-        <v>2.9750000000000001</v>
-      </c>
-      <c r="F5" s="44">
-        <f t="shared" si="0"/>
         <v>2.8235294117647061</v>
       </c>
-      <c r="G5" s="13">
+      <c r="G5" s="59">
         <v>968</v>
       </c>
       <c r="H5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="8"/>
         <v>332</v>
       </c>
-      <c r="I5" s="14">
+      <c r="I5" s="56">
         <v>15</v>
       </c>
-      <c r="J5" s="49">
-        <f t="shared" si="2"/>
+      <c r="J5" s="67">
+        <f t="shared" si="9"/>
         <v>0.375</v>
       </c>
-      <c r="K5" s="52">
-        <f t="shared" si="3"/>
+      <c r="K5" s="68">
+        <f t="shared" si="10"/>
         <v>0.34297520661157027</v>
       </c>
-      <c r="L5" s="46">
-        <f t="shared" si="4"/>
+      <c r="L5" s="62">
+        <f t="shared" si="11"/>
         <v>251.07692307692307</v>
       </c>
-      <c r="M5" s="54">
-        <f t="shared" si="5"/>
+      <c r="M5" s="69">
+        <f t="shared" si="12"/>
         <v>247.21230769230769</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A6" s="7">
+    <row r="6">
+      <c r="A6" s="55">
         <v>1400</v>
       </c>
-      <c r="B6" s="13">
+      <c r="B6">
         <f>32.9*10</f>
         <v>329</v>
       </c>
       <c r="C6">
+        <f t="shared" si="13"/>
+        <v>1071</v>
+      </c>
+      <c r="D6" s="56">
+        <v>137</v>
+      </c>
+      <c r="E6" s="57">
         <f t="shared" si="6"/>
-        <v>1071</v>
-      </c>
-      <c r="D6" s="14">
-        <v>137</v>
-      </c>
-      <c r="E6" s="42">
+        <v>3.4249999999999998</v>
+      </c>
+      <c r="F6" s="58">
         <f t="shared" si="7"/>
-        <v>3.4249999999999998</v>
-      </c>
-      <c r="F6" s="44">
-        <f t="shared" si="0"/>
         <v>3.2553191489361701</v>
       </c>
-      <c r="G6" s="13">
+      <c r="G6" s="59">
         <v>1074</v>
       </c>
       <c r="H6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="8"/>
         <v>326</v>
       </c>
-      <c r="I6" s="14">
+      <c r="I6" s="56">
         <v>13</v>
       </c>
-      <c r="J6" s="49">
-        <f t="shared" si="2"/>
+      <c r="J6" s="67">
+        <f t="shared" si="9"/>
         <v>0.32500000000000001</v>
       </c>
-      <c r="K6" s="52">
-        <f t="shared" si="3"/>
+      <c r="K6" s="68">
+        <f t="shared" si="10"/>
         <v>0.30353817504655495</v>
       </c>
-      <c r="L6" s="46">
-        <f t="shared" si="4"/>
+      <c r="L6" s="62">
+        <f t="shared" si="11"/>
         <v>251.685</v>
       </c>
-      <c r="M6" s="54">
-        <f t="shared" si="5"/>
+      <c r="M6" s="69">
+        <f t="shared" si="12"/>
         <v>250.08857142857144</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A7" s="7">
+    <row r="7">
+      <c r="A7" s="11">
         <v>1500</v>
       </c>
-      <c r="B7" s="17">
+      <c r="B7" s="70">
         <f>31.9*10</f>
         <v>319</v>
       </c>
-      <c r="C7" s="18">
+      <c r="C7" s="70">
+        <f t="shared" si="13"/>
+        <v>1181</v>
+      </c>
+      <c r="D7" s="71">
+        <v>155</v>
+      </c>
+      <c r="E7" s="72">
         <f t="shared" si="6"/>
-        <v>1181</v>
-      </c>
-      <c r="D7" s="19">
-        <v>155</v>
-      </c>
-      <c r="E7" s="43">
+        <v>3.875</v>
+      </c>
+      <c r="F7" s="73">
         <f t="shared" si="7"/>
-        <v>3.875</v>
-      </c>
-      <c r="F7" s="45">
-        <f t="shared" si="0"/>
         <v>3.7021943573667713</v>
       </c>
-      <c r="G7" s="17">
+      <c r="G7" s="74">
         <v>1186</v>
       </c>
-      <c r="H7" s="18">
-        <f t="shared" si="1"/>
+      <c r="H7" s="70">
+        <f t="shared" si="8"/>
         <v>314</v>
       </c>
-      <c r="I7" s="19">
+      <c r="I7" s="71">
         <v>12</v>
       </c>
-      <c r="J7" s="50">
-        <f t="shared" si="2"/>
-        <v>0.3</v>
-      </c>
-      <c r="K7" s="53">
-        <f t="shared" si="3"/>
+      <c r="J7" s="75">
+        <f t="shared" si="9"/>
+        <v>0.29999999999999999</v>
+      </c>
+      <c r="K7" s="76">
+        <f t="shared" si="10"/>
         <v>0.26475548060708265</v>
       </c>
-      <c r="L7" s="47">
-        <f t="shared" si="4"/>
+      <c r="L7" s="77">
+        <f t="shared" si="11"/>
         <v>251.15933333333334</v>
       </c>
-      <c r="M7" s="55">
-        <f t="shared" si="5"/>
+      <c r="M7" s="78">
+        <f t="shared" si="12"/>
         <v>248.26933333333332</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="L13" s="3"/>
+    <row r="13">
+      <c r="L13" s="20"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="4">
     <mergeCell ref="B1:F1"/>
     <mergeCell ref="G1:K1"/>
+    <mergeCell ref="O2:P2"/>
+    <mergeCell ref="O3:P3"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:O8"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="9.46484375" customWidth="1"/>
-    <col min="8" max="8" width="9.86328125" customWidth="1"/>
-    <col min="9" max="10" width="11.19921875" customWidth="1"/>
-    <col min="12" max="12" width="18.53125" customWidth="1"/>
-    <col min="13" max="13" width="18.265625" customWidth="1"/>
-    <col min="14" max="14" width="16.3984375" customWidth="1"/>
-    <col min="15" max="15" width="14.53125" customWidth="1"/>
+    <col customWidth="1" min="2" max="2" width="9.46484375"/>
+    <col customWidth="1" min="8" max="8" width="9.86328125"/>
+    <col customWidth="1" min="9" max="10" width="11.19921875"/>
+    <col bestFit="1" customWidth="1" min="12" max="13" width="19.04296875"/>
+    <col bestFit="1" customWidth="1" min="14" max="14" width="14.453125"/>
+    <col bestFit="1" customWidth="1" min="15" max="15" width="9.00390625"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="B1" s="35" t="s">
+    <row r="1">
+      <c r="B1" s="44" t="s">
         <v>23</v>
       </c>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="37"/>
-      <c r="G1" s="39" t="s">
+      <c r="C1" s="45"/>
+      <c r="D1" s="45"/>
+      <c r="E1" s="45"/>
+      <c r="F1" s="46"/>
+      <c r="G1" s="79" t="s">
         <v>24</v>
       </c>
-      <c r="H1" s="40"/>
-      <c r="I1" s="40"/>
-      <c r="J1" s="40"/>
-      <c r="K1" s="41"/>
-    </row>
-    <row r="2" spans="1:15" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="7" t="s">
+      <c r="H1" s="80"/>
+      <c r="I1" s="80"/>
+      <c r="J1" s="80"/>
+      <c r="K1" s="81"/>
+    </row>
+    <row r="2" ht="13">
+      <c r="A2" s="82" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="83" t="s">
         <v>26</v>
       </c>
-      <c r="C2" s="21" t="s">
+      <c r="C2" s="83" t="s">
         <v>27</v>
       </c>
-      <c r="D2" s="22" t="s">
+      <c r="D2" s="84" t="s">
         <v>37</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="E2" s="51" t="s">
         <v>29</v>
       </c>
-      <c r="F2" s="10" t="s">
+      <c r="F2" s="50" t="s">
         <v>30</v>
       </c>
-      <c r="G2" s="20" t="s">
+      <c r="G2" s="85" t="s">
         <v>26</v>
       </c>
-      <c r="H2" s="21" t="s">
+      <c r="H2" s="83" t="s">
         <v>27</v>
       </c>
-      <c r="I2" s="23" t="s">
+      <c r="I2" s="86" t="s">
         <v>37</v>
       </c>
-      <c r="J2" s="8" t="s">
+      <c r="J2" s="51" t="s">
         <v>29</v>
       </c>
-      <c r="K2" s="10" t="s">
+      <c r="K2" s="50" t="s">
         <v>30</v>
       </c>
-      <c r="L2" s="24" t="s">
+      <c r="L2" s="87" t="s">
         <v>31</v>
       </c>
-      <c r="M2" s="10" t="s">
+      <c r="M2" s="50" t="s">
         <v>32</v>
       </c>
-      <c r="N2" s="25" t="s">
+      <c r="N2" s="88" t="s">
         <v>33</v>
       </c>
-      <c r="O2" s="26" t="s">
+      <c r="O2" s="89" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A3" s="27">
+      <c r="P2" s="90"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="91">
         <v>600</v>
       </c>
-      <c r="B3" s="28">
+      <c r="B3" s="92">
         <v>139</v>
       </c>
-      <c r="C3" s="29">
-        <f t="shared" ref="C3:C6" si="0">A3-B3</f>
+      <c r="C3" s="93">
+        <f t="shared" ref="C3:C6" si="14">A3-B3</f>
         <v>461</v>
       </c>
-      <c r="D3" s="16">
+      <c r="D3" s="94">
         <v>146</v>
       </c>
-      <c r="E3" s="15">
-        <f t="shared" ref="E3:E6" si="1">D3/40</f>
-        <v>3.65</v>
-      </c>
-      <c r="F3" s="16">
-        <f t="shared" ref="F3:F6" si="2">C3/B3</f>
+      <c r="E3" s="95">
+        <f t="shared" ref="E3:E6" si="15">D3/40</f>
+        <v>3.6499999999999999</v>
+      </c>
+      <c r="F3" s="94">
+        <f t="shared" ref="F3:F6" si="16">C3/B3</f>
         <v>3.3165467625899279</v>
       </c>
-      <c r="G3" s="15">
+      <c r="G3" s="95">
         <v>467</v>
       </c>
-      <c r="H3" s="29">
-        <f t="shared" ref="H3:H6" si="3">A3-G3</f>
+      <c r="H3" s="93">
+        <f t="shared" ref="H3:H6" si="17">A3-G3</f>
         <v>133</v>
       </c>
-      <c r="I3" s="16">
+      <c r="I3" s="94">
         <v>13</v>
       </c>
-      <c r="J3" s="15">
-        <f t="shared" ref="J3:J6" si="4">I3/40</f>
+      <c r="J3" s="95">
+        <f t="shared" ref="J3:J6" si="18">I3/40</f>
         <v>0.32500000000000001</v>
       </c>
-      <c r="K3" s="16">
-        <f t="shared" ref="K3:K6" si="5">H3/G3</f>
+      <c r="K3" s="94">
+        <f t="shared" ref="K3:K6" si="19">H3/G3</f>
         <v>0.28479657387580298</v>
       </c>
-      <c r="L3" s="59">
-        <f t="shared" ref="L3:L6" si="6">(B3*C3)/(B3+C3)</f>
+      <c r="L3" s="96">
+        <f t="shared" ref="L3:L6" si="20">(B3*C3)/(B3+C3)</f>
         <v>106.79833333333333</v>
       </c>
-      <c r="M3" s="60">
-        <f t="shared" ref="M3:M6" si="7">(G3*H3)/(G3+H3)</f>
+      <c r="M3" s="97">
+        <f t="shared" ref="M3:M6" si="21">(G3*H3)/(G3+H3)</f>
         <v>103.51833333333333</v>
       </c>
-      <c r="N3" s="30" t="s">
+      <c r="N3" s="98" t="s">
         <v>38</v>
       </c>
-      <c r="O3" s="30" t="s">
+      <c r="O3" s="99" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A4" s="31">
+      <c r="P3" s="66"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="91">
         <v>550</v>
       </c>
-      <c r="B4" s="32">
+      <c r="B4" s="63">
         <v>146</v>
       </c>
       <c r="C4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v>404</v>
       </c>
-      <c r="D4" s="14">
+      <c r="D4" s="56">
         <v>120</v>
       </c>
-      <c r="E4" s="13">
-        <f t="shared" si="1"/>
+      <c r="E4" s="59">
+        <f t="shared" si="15"/>
         <v>3</v>
       </c>
-      <c r="F4" s="14">
-        <f t="shared" si="2"/>
+      <c r="F4" s="56">
+        <f t="shared" si="16"/>
         <v>2.7671232876712328</v>
       </c>
-      <c r="G4" s="13">
+      <c r="G4" s="59">
         <v>413</v>
       </c>
       <c r="H4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="17"/>
         <v>137</v>
       </c>
-      <c r="I4" s="14">
+      <c r="I4" s="56">
         <v>15</v>
       </c>
-      <c r="J4" s="13">
-        <f t="shared" si="4"/>
+      <c r="J4" s="59">
+        <f t="shared" si="18"/>
         <v>0.375</v>
       </c>
-      <c r="K4" s="14">
-        <f t="shared" si="5"/>
+      <c r="K4" s="56">
+        <f t="shared" si="19"/>
         <v>0.33171912832929784</v>
       </c>
-      <c r="L4" s="54">
-        <f t="shared" si="6"/>
+      <c r="L4" s="69">
+        <f t="shared" si="20"/>
         <v>107.24363636363637</v>
       </c>
-      <c r="M4" s="61">
-        <f t="shared" si="7"/>
+      <c r="M4" s="100">
+        <f t="shared" si="21"/>
         <v>102.87454545454545</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A5" s="31">
+    <row r="5">
+      <c r="A5" s="91">
         <v>500</v>
       </c>
-      <c r="B5" s="32">
+      <c r="B5" s="63">
         <v>155</v>
       </c>
       <c r="C5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="14"/>
         <v>345</v>
       </c>
-      <c r="D5" s="14">
+      <c r="D5" s="56">
         <v>98</v>
       </c>
-      <c r="E5" s="13">
-        <f t="shared" si="1"/>
+      <c r="E5" s="59">
+        <f t="shared" si="15"/>
         <v>2.4500000000000002</v>
       </c>
-      <c r="F5" s="14">
-        <f t="shared" si="2"/>
+      <c r="F5" s="56">
+        <f t="shared" si="16"/>
         <v>2.225806451612903</v>
       </c>
-      <c r="G5" s="13">
+      <c r="G5" s="59">
         <v>355</v>
       </c>
       <c r="H5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="17"/>
         <v>145</v>
       </c>
-      <c r="I5" s="14">
+      <c r="I5" s="56">
         <v>19</v>
       </c>
-      <c r="J5" s="13">
-        <f t="shared" si="4"/>
+      <c r="J5" s="59">
+        <f t="shared" si="18"/>
         <v>0.47499999999999998</v>
       </c>
-      <c r="K5" s="14">
-        <f t="shared" si="5"/>
+      <c r="K5" s="56">
+        <f t="shared" si="19"/>
         <v>0.40845070422535212</v>
       </c>
-      <c r="L5" s="54">
-        <f t="shared" si="6"/>
+      <c r="L5" s="69">
+        <f t="shared" si="20"/>
         <v>106.95</v>
       </c>
-      <c r="M5" s="61">
-        <f t="shared" si="7"/>
+      <c r="M5" s="100">
+        <f t="shared" si="21"/>
         <v>102.95</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A6" s="33">
+    <row r="6">
+      <c r="A6" s="101">
         <v>450</v>
       </c>
-      <c r="B6" s="34">
+      <c r="B6" s="102">
         <v>173</v>
       </c>
-      <c r="C6" s="18">
-        <f t="shared" si="0"/>
+      <c r="C6" s="70">
+        <f t="shared" si="14"/>
         <v>277</v>
       </c>
-      <c r="D6" s="19">
+      <c r="D6" s="71">
         <v>68</v>
       </c>
-      <c r="E6" s="17">
-        <f t="shared" si="1"/>
+      <c r="E6" s="74">
+        <f t="shared" si="15"/>
         <v>1.7</v>
       </c>
-      <c r="F6" s="19">
-        <f t="shared" si="2"/>
+      <c r="F6" s="71">
+        <f t="shared" si="16"/>
         <v>1.6011560693641618</v>
       </c>
-      <c r="G6" s="17">
+      <c r="G6" s="74">
         <v>285</v>
       </c>
-      <c r="H6" s="18">
-        <f t="shared" si="3"/>
+      <c r="H6" s="70">
+        <f t="shared" si="17"/>
         <v>165</v>
       </c>
-      <c r="I6" s="19">
+      <c r="I6" s="71">
         <v>26</v>
       </c>
-      <c r="J6" s="17">
-        <f t="shared" si="4"/>
-        <v>0.65</v>
-      </c>
-      <c r="K6" s="19">
-        <f t="shared" si="5"/>
+      <c r="J6" s="74">
+        <f t="shared" si="18"/>
+        <v>0.65000000000000002</v>
+      </c>
+      <c r="K6" s="71">
+        <f t="shared" si="19"/>
         <v>0.57894736842105265</v>
       </c>
-      <c r="L6" s="55">
-        <f t="shared" si="6"/>
+      <c r="L6" s="78">
+        <f t="shared" si="20"/>
         <v>106.49111111111111</v>
       </c>
-      <c r="M6" s="62">
-        <f t="shared" si="7"/>
+      <c r="M6" s="103">
+        <f t="shared" si="21"/>
         <v>104.5</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="D8" s="3"/>
+    <row r="8">
+      <c r="D8" s="20"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="4">
     <mergeCell ref="B1:F1"/>
     <mergeCell ref="G1:K1"/>
+    <mergeCell ref="O2:P2"/>
+    <mergeCell ref="O3:P3"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>